--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60A8ACB1-D598-4DC1-8B44-D0D6F963F93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3EBD58C-AEF9-4B8A-B9DD-2165A2BC1D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -206,6 +206,27 @@
   </si>
   <si>
     <t>MCA / D1P2631</t>
+  </si>
+  <si>
+    <t>Today, I worked on some Python programs.</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Today, I worked on some C++ and Python programs.</t>
+  </si>
+  <si>
+    <t>Today, I worked on some Java and Python programs.</t>
   </si>
 </sst>
 </file>
@@ -1032,93 +1053,189 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>46246</v>
+      </c>
+      <c r="B7" s="9">
+        <v>360</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9">
+        <v>60</v>
+      </c>
+      <c r="E7" s="9">
+        <v>100</v>
+      </c>
+      <c r="F7" s="9">
+        <v>350</v>
+      </c>
+      <c r="G7" s="9">
+        <v>7</v>
+      </c>
+      <c r="H7" s="9">
+        <v>60</v>
+      </c>
+      <c r="I7" s="10">
+        <f t="shared" ref="I7:I10" si="2">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <v>930</v>
+      </c>
+      <c r="J7" s="10">
+        <f t="shared" ref="J7:J10" si="3">IF(I7="","",1440-I7)</f>
+        <v>510</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B8" s="9">
+        <v>420</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9">
+        <v>60</v>
+      </c>
+      <c r="E8" s="9">
+        <v>60</v>
+      </c>
+      <c r="F8" s="9">
+        <v>150</v>
+      </c>
+      <c r="G8" s="9">
+        <v>3</v>
+      </c>
+      <c r="H8" s="9">
+        <v>60</v>
+      </c>
+      <c r="I8" s="10">
+        <f t="shared" si="2"/>
+        <v>750</v>
+      </c>
+      <c r="J8" s="10">
+        <f t="shared" si="3"/>
+        <v>690</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B9" s="9">
+        <v>360</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9">
+        <v>60</v>
+      </c>
+      <c r="E9" s="9">
+        <v>120</v>
+      </c>
+      <c r="F9" s="9">
+        <v>250</v>
+      </c>
+      <c r="G9" s="9">
+        <v>5</v>
+      </c>
+      <c r="H9" s="9">
+        <v>60</v>
+      </c>
+      <c r="I9" s="10">
+        <f t="shared" si="2"/>
+        <v>850</v>
+      </c>
+      <c r="J9" s="10">
+        <f t="shared" si="3"/>
+        <v>590</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>46249</v>
+      </c>
+      <c r="B10" s="9">
+        <v>480</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>60</v>
+      </c>
+      <c r="E10" s="9">
+        <v>300</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>60</v>
+      </c>
+      <c r="I10" s="10">
+        <f t="shared" si="2"/>
+        <v>900</v>
+      </c>
+      <c r="J10" s="10">
+        <f t="shared" si="3"/>
+        <v>540</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
@@ -2428,11 +2545,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2450,11 +2567,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2472,11 +2589,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2494,11 +2611,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2516,11 +2633,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2538,11 +2655,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2560,11 +2677,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2582,11 +2699,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2604,11 +2721,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2626,11 +2743,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -2648,11 +2765,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -2670,11 +2787,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -2692,11 +2809,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -2714,11 +2831,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -2736,11 +2853,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -2758,11 +2875,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -2780,11 +2897,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -2802,11 +2919,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -2824,11 +2941,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -2846,11 +2963,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -2868,11 +2985,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -2890,11 +3007,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -2912,11 +3029,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -2934,11 +3051,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -2956,11 +3073,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -2978,11 +3095,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3000,11 +3117,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3022,11 +3139,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3044,11 +3161,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3066,11 +3183,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3088,11 +3205,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3110,11 +3227,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3132,11 +3249,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3154,11 +3271,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3176,11 +3293,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3198,11 +3315,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3220,11 +3337,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3242,11 +3359,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3264,11 +3381,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3286,11 +3403,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3308,11 +3425,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3330,11 +3447,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3352,11 +3469,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3374,11 +3491,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3396,11 +3513,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3418,11 +3535,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3440,11 +3557,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3462,11 +3579,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3484,11 +3601,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3506,11 +3623,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3528,11 +3645,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3550,11 +3667,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3572,11 +3689,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3594,11 +3711,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3616,11 +3733,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -3638,11 +3755,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -3660,11 +3777,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -3682,11 +3799,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -3704,11 +3821,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -3726,11 +3843,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -3748,11 +3865,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -3770,11 +3887,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -3792,11 +3909,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -3814,11 +3931,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -3836,11 +3953,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -3858,11 +3975,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -3880,11 +3997,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -3902,11 +4019,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -3924,11 +4041,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -3946,11 +4063,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -3968,11 +4085,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -3990,11 +4107,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4012,11 +4129,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4034,11 +4151,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4056,11 +4173,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4078,11 +4195,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4100,11 +4217,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4122,11 +4239,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4144,11 +4261,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4166,11 +4283,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4188,11 +4305,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4210,11 +4327,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4232,11 +4349,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4254,11 +4371,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4276,11 +4393,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4298,11 +4415,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4320,11 +4437,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4342,11 +4459,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4364,11 +4481,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4386,11 +4503,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4408,11 +4525,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4430,11 +4547,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4452,11 +4569,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4474,11 +4591,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4496,11 +4613,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4518,11 +4635,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4540,11 +4657,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4562,11 +4679,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4584,11 +4701,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4606,11 +4723,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4628,11 +4745,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -4650,11 +4767,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -4672,11 +4789,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -4694,11 +4811,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -4716,11 +4833,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -4738,11 +4855,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -4760,11 +4877,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -4782,11 +4899,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -4804,11 +4921,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -4826,11 +4943,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -4848,11 +4965,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -4870,11 +4987,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -4892,11 +5009,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -4914,11 +5031,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -4936,11 +5053,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -4958,11 +5075,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -4980,11 +5097,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5002,11 +5119,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5024,11 +5141,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5046,11 +5163,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5068,11 +5185,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5090,11 +5207,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5112,11 +5229,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5134,11 +5251,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5156,11 +5273,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5178,11 +5295,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5200,11 +5317,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5222,11 +5339,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5244,11 +5361,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5266,11 +5383,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5288,11 +5405,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5310,11 +5427,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5332,11 +5449,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5354,11 +5471,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5376,11 +5493,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5398,11 +5515,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5420,11 +5537,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5442,11 +5559,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5464,11 +5581,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5486,11 +5603,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5508,11 +5625,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5530,11 +5647,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5552,11 +5669,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5574,11 +5691,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5596,11 +5713,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5618,11 +5735,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -5640,11 +5757,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -5662,11 +5779,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -5684,11 +5801,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -5706,11 +5823,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -5728,11 +5845,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -5750,11 +5867,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -5772,11 +5889,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -5794,11 +5911,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -5816,11 +5933,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -5838,11 +5955,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -5860,11 +5977,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -5882,11 +5999,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -5904,11 +6021,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -5926,11 +6043,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -5948,11 +6065,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -5970,11 +6087,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -5992,11 +6109,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6014,11 +6131,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6036,11 +6153,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6058,11 +6175,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6080,11 +6197,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6102,11 +6219,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6124,11 +6241,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6146,11 +6263,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6168,11 +6285,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6190,11 +6307,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6212,11 +6329,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6234,11 +6351,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6256,11 +6373,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6278,11 +6395,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6300,11 +6417,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6322,11 +6439,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6344,11 +6461,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6366,11 +6483,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6388,11 +6505,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6410,11 +6527,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6432,11 +6549,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6454,11 +6571,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6476,11 +6593,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6498,11 +6615,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6520,11 +6637,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6542,11 +6659,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6564,11 +6681,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6586,11 +6703,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6608,11 +6725,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6630,11 +6747,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6652,11 +6769,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -6674,11 +6791,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -6696,11 +6813,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -6718,11 +6835,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -6740,11 +6857,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -6762,11 +6879,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -6784,11 +6901,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -6806,11 +6923,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -6828,11 +6945,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -6850,11 +6967,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -6872,11 +6989,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -6894,11 +7011,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -6916,11 +7033,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -6938,11 +7055,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -6960,11 +7077,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -6982,11 +7099,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7004,11 +7121,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7026,11 +7143,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7048,11 +7165,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7070,11 +7187,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7092,11 +7209,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7114,11 +7231,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7136,11 +7253,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7158,11 +7275,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7180,11 +7297,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7202,11 +7319,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7224,11 +7341,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7246,11 +7363,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7268,11 +7385,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7290,11 +7407,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7312,11 +7429,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7334,11 +7451,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7356,11 +7473,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7378,11 +7495,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7400,11 +7517,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7422,11 +7539,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7444,11 +7561,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7466,11 +7583,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7488,11 +7605,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7510,11 +7627,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7532,11 +7649,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7554,11 +7671,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7576,11 +7693,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7598,11 +7715,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7620,11 +7737,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -7642,11 +7759,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -7664,11 +7781,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -7686,11 +7803,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -7708,11 +7825,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -7730,11 +7847,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -7752,11 +7869,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -7774,11 +7891,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -7796,11 +7913,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -7818,11 +7935,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -7840,11 +7957,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -7862,11 +7979,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -7884,11 +8001,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -7906,11 +8023,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -7928,11 +8045,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -7950,11 +8067,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -7972,11 +8089,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -7994,11 +8111,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8016,11 +8133,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8038,11 +8155,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8060,11 +8177,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8082,11 +8199,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8104,11 +8221,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8126,11 +8243,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8148,11 +8265,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8170,11 +8287,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8192,11 +8309,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8214,11 +8331,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8236,11 +8353,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8258,11 +8375,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8280,11 +8397,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8302,11 +8419,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8324,11 +8441,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8346,11 +8463,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8368,11 +8485,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8390,11 +8507,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8412,11 +8529,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8434,11 +8551,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8456,11 +8573,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8478,11 +8595,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8500,11 +8617,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8522,11 +8639,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8544,11 +8661,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8566,11 +8683,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8588,11 +8705,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8610,11 +8727,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8632,11 +8749,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -8654,11 +8771,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -8676,11 +8793,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -8698,11 +8815,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -8720,11 +8837,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -8742,11 +8859,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -8764,11 +8881,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -8786,11 +8903,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -8808,11 +8925,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -8830,11 +8947,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -8852,11 +8969,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -8874,11 +8991,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -8896,11 +9013,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -8918,11 +9035,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -8940,11 +9057,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -8962,11 +9079,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -8984,11 +9101,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9006,11 +9123,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9028,11 +9145,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9050,11 +9167,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9072,11 +9189,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9094,11 +9211,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9116,11 +9233,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9138,11 +9255,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9160,11 +9277,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9182,11 +9299,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9204,11 +9321,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9226,11 +9343,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9248,11 +9365,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9270,11 +9387,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9292,11 +9409,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9314,11 +9431,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9336,11 +9453,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9358,11 +9475,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9380,11 +9497,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9402,11 +9519,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9424,11 +9541,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9446,11 +9563,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9468,11 +9585,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9490,11 +9607,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9512,11 +9629,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9534,11 +9651,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9556,11 +9673,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9578,11 +9695,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9600,11 +9717,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -9622,11 +9739,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -9644,11 +9761,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -9666,11 +9783,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -9688,11 +9805,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -9710,11 +9827,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70EA5A52-3A38-4591-AEC5-E6F275506179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF91D62A-F042-4CC6-BBE8-A277CF8B7EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -231,6 +231,9 @@
   <si>
     <t>Today, I worked on DSA Java programs.</t>
   </si>
+  <si>
+    <t>Today, I worked on DSA Java programs and MySQL.</t>
+  </si>
 </sst>
 </file>
 
@@ -394,9 +397,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -412,6 +412,9 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -897,74 +900,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="20">
         <v>12625731</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="15"/>
+      <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1011,302 +1014,326 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="16">
+      <c r="A6" s="13">
         <v>46245</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="14">
         <v>420</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="14">
         <v>0</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="14">
         <v>60</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="14">
         <v>60</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="14">
         <v>250</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="14">
         <v>5</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="14">
         <v>60</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="15">
         <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>850</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="15">
         <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
         <v>590</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="19" t="s">
+      <c r="M6" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N6" s="20" t="s">
+      <c r="N6" s="17" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="16">
+      <c r="A7" s="13">
         <v>46246</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="14">
         <v>360</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="14">
         <v>0</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="14">
         <v>60</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="14">
         <v>100</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="14">
         <v>350</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="14">
         <v>7</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="14">
         <v>60</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="15">
         <f t="shared" ref="I7:I10" si="2">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
         <v>930</v>
       </c>
-      <c r="J7" s="18">
+      <c r="J7" s="15">
         <f t="shared" ref="J7:J10" si="3">IF(I7="","",1440-I7)</f>
         <v>510</v>
       </c>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="M7" s="19" t="s">
+      <c r="M7" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="20" t="s">
+      <c r="N7" s="17" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="16">
+      <c r="A8" s="13">
         <v>46247</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="14">
         <v>420</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="14">
         <v>0</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="14">
         <v>60</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="14">
         <v>60</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="14">
         <v>150</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="14">
         <v>3</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="14">
         <v>60</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="15">
         <f t="shared" si="2"/>
         <v>750</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="15">
         <f t="shared" si="3"/>
         <v>690</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="K8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M8" s="19" t="s">
+      <c r="M8" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N8" s="20" t="s">
+      <c r="N8" s="17" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="16">
+      <c r="A9" s="13">
         <v>46248</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="14">
         <v>360</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="14">
         <v>0</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="14">
         <v>60</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="14">
         <v>120</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="14">
         <v>250</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="14">
         <v>5</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="14">
         <v>60</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="15">
         <f t="shared" si="2"/>
         <v>850</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="15">
         <f t="shared" si="3"/>
         <v>590</v>
       </c>
-      <c r="K9" s="19" t="s">
+      <c r="K9" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L9" s="19" t="s">
+      <c r="L9" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="19" t="s">
+      <c r="M9" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="20" t="s">
+      <c r="N9" s="17" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="16">
+      <c r="A10" s="13">
         <v>46249</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="14">
         <v>480</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="14">
         <v>0</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="14">
         <v>60</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="14">
         <v>300</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="14">
         <v>0</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="14">
         <v>0</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="14">
         <v>60</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="15">
         <f t="shared" si="2"/>
         <v>900</v>
       </c>
-      <c r="J10" s="18">
+      <c r="J10" s="15">
         <f t="shared" si="3"/>
         <v>540</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="M10" s="19" t="s">
+      <c r="M10" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N10" s="20" t="s">
+      <c r="N10" s="17" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="16">
+      <c r="A11" s="13">
         <v>46250</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="14">
         <v>450</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="14">
         <v>0</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="14">
         <v>90</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="14">
         <v>240</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="14">
         <v>0</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="14">
         <v>0</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="14">
         <v>60</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="15">
         <f t="shared" ref="I11" si="4">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
         <v>840</v>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="15">
         <f t="shared" ref="J11" si="5">IF(I11="","",1440-I11)</f>
         <v>600</v>
       </c>
-      <c r="K11" s="19" t="s">
+      <c r="K11" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L11" s="19" t="s">
+      <c r="L11" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="19" t="s">
+      <c r="M11" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N11" s="20" t="s">
+      <c r="N11" s="17" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="12"/>
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B12" s="14">
+        <v>450</v>
+      </c>
+      <c r="C12" s="14">
+        <v>15</v>
+      </c>
+      <c r="D12" s="14">
+        <v>90</v>
+      </c>
+      <c r="E12" s="14">
+        <v>150</v>
+      </c>
+      <c r="F12" s="14">
+        <v>350</v>
+      </c>
+      <c r="G12" s="14">
+        <v>7</v>
+      </c>
+      <c r="H12" s="14">
+        <v>50</v>
+      </c>
+      <c r="I12" s="15">
+        <f t="shared" ref="I12" si="6">IF(SUM(B12:F12,H12)=0,"",SUM(B12:F12,H12))</f>
+        <v>1105</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" ref="J12" si="7">IF(I12="","",1440-I12)</f>
+        <v>335</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
@@ -1362,7 +1389,7 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
         <v/>
       </c>
       <c r="J15" s="10" t="str">
@@ -2572,11 +2599,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="8">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="9">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -2594,11 +2621,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -2616,11 +2643,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -2638,11 +2665,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -2660,11 +2687,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -2682,11 +2709,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -2704,11 +2731,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -2726,11 +2753,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -2748,11 +2775,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -2770,11 +2797,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -2792,11 +2819,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -2814,11 +2841,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -2836,11 +2863,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -2858,11 +2885,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -2880,11 +2907,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -2902,11 +2929,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -2924,11 +2951,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -2946,11 +2973,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -2968,11 +2995,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -2990,11 +3017,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3012,11 +3039,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3034,11 +3061,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3056,11 +3083,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3078,11 +3105,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3100,11 +3127,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3122,11 +3149,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3144,11 +3171,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3166,11 +3193,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3188,11 +3215,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3210,11 +3237,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3232,11 +3259,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3254,11 +3281,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3276,11 +3303,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3298,11 +3325,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3320,11 +3347,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3342,11 +3369,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3364,11 +3391,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3386,11 +3413,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3408,11 +3435,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3430,11 +3457,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3452,11 +3479,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3474,11 +3501,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3496,11 +3523,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3518,11 +3545,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3540,11 +3567,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3562,11 +3589,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3584,11 +3611,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -3606,11 +3633,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -3628,11 +3655,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -3650,11 +3677,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -3672,11 +3699,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -3694,11 +3721,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -3716,11 +3743,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -3738,11 +3765,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -3760,11 +3787,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -3782,11 +3809,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -3804,11 +3831,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -3826,11 +3853,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -3848,11 +3875,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -3870,11 +3897,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -3892,11 +3919,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -3914,11 +3941,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -3936,11 +3963,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -3958,11 +3985,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -3980,11 +4007,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="10">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="11">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4002,11 +4029,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4024,11 +4051,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4046,11 +4073,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4068,11 +4095,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4090,11 +4117,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4112,11 +4139,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4134,11 +4161,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4156,11 +4183,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4178,11 +4205,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4200,11 +4227,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4222,11 +4249,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4244,11 +4271,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4266,11 +4293,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4288,11 +4315,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4310,11 +4337,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4332,11 +4359,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4354,11 +4381,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4376,11 +4403,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4398,11 +4425,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4420,11 +4447,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4442,11 +4469,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4464,11 +4491,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4486,11 +4513,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4508,11 +4535,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -4530,11 +4557,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -4552,11 +4579,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -4574,11 +4601,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -4596,11 +4623,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -4618,11 +4645,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -4640,11 +4667,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -4662,11 +4689,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -4684,11 +4711,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -4706,11 +4733,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -4728,11 +4755,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -4750,11 +4777,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -4772,11 +4799,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -4794,11 +4821,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -4816,11 +4843,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -4838,11 +4865,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -4860,11 +4887,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -4882,11 +4909,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -4904,11 +4931,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -4926,11 +4953,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -4948,11 +4975,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -4970,11 +4997,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -4992,11 +5019,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5014,11 +5041,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5036,11 +5063,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5058,11 +5085,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5080,11 +5107,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5102,11 +5129,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5124,11 +5151,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5146,11 +5173,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5168,11 +5195,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5190,11 +5217,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5212,11 +5239,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5234,11 +5261,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5256,11 +5283,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5278,11 +5305,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5300,11 +5327,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5322,11 +5349,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5344,11 +5371,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5366,11 +5393,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5388,11 +5415,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="12">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="13">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5410,11 +5437,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5432,11 +5459,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5454,11 +5481,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5476,11 +5503,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5498,11 +5525,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -5520,11 +5547,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -5542,11 +5569,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -5564,11 +5591,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -5586,11 +5613,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -5608,11 +5635,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -5630,11 +5657,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -5652,11 +5679,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -5674,11 +5701,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -5696,11 +5723,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -5718,11 +5745,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -5740,11 +5767,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -5762,11 +5789,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -5784,11 +5811,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -5806,11 +5833,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -5828,11 +5855,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -5850,11 +5877,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -5872,11 +5899,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -5894,11 +5921,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -5916,11 +5943,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -5938,11 +5965,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -5960,11 +5987,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -5982,11 +6009,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6004,11 +6031,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6026,11 +6053,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6048,11 +6075,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6070,11 +6097,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6092,11 +6119,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6114,11 +6141,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6136,11 +6163,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6158,11 +6185,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6180,11 +6207,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6202,11 +6229,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6224,11 +6251,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6246,11 +6273,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6268,11 +6295,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6290,11 +6317,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6312,11 +6339,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6334,11 +6361,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6356,11 +6383,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6378,11 +6405,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6400,11 +6427,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6422,11 +6449,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6444,11 +6471,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6466,11 +6493,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6488,11 +6515,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6510,11 +6537,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -6532,11 +6559,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -6554,11 +6581,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -6576,11 +6603,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -6598,11 +6625,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -6620,11 +6647,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -6642,11 +6669,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -6664,11 +6691,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -6686,11 +6713,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -6708,11 +6735,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -6730,11 +6757,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -6752,11 +6779,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -6774,11 +6801,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -6796,11 +6823,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="14">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="15">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -6818,11 +6845,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -6840,11 +6867,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -6862,11 +6889,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -6884,11 +6911,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -6906,11 +6933,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -6928,11 +6955,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -6950,11 +6977,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -6972,11 +6999,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -6994,11 +7021,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7016,11 +7043,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7038,11 +7065,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7060,11 +7087,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7082,11 +7109,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7104,11 +7131,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7126,11 +7153,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7148,11 +7175,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7170,11 +7197,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7192,11 +7219,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7214,11 +7241,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7236,11 +7263,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7258,11 +7285,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7280,11 +7307,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7302,11 +7329,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7324,11 +7351,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7346,11 +7373,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7368,11 +7395,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7390,11 +7417,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7412,11 +7439,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7434,11 +7461,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7456,11 +7483,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7478,11 +7505,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7500,11 +7527,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -7522,11 +7549,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -7544,11 +7571,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -7566,11 +7593,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -7588,11 +7615,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -7610,11 +7637,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -7632,11 +7659,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -7654,11 +7681,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -7676,11 +7703,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -7698,11 +7725,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -7720,11 +7747,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -7742,11 +7769,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -7764,11 +7791,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -7786,11 +7813,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -7808,11 +7835,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -7830,11 +7857,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -7852,11 +7879,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -7874,11 +7901,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -7896,11 +7923,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -7918,11 +7945,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -7940,11 +7967,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -7962,11 +7989,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -7984,11 +8011,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8006,11 +8033,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8028,11 +8055,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8050,11 +8077,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8072,11 +8099,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8094,11 +8121,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8116,11 +8143,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8138,11 +8165,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8160,11 +8187,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8182,11 +8209,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8204,11 +8231,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="16">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="17">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8226,11 +8253,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8248,11 +8275,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8270,11 +8297,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8292,11 +8319,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8314,11 +8341,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8336,11 +8363,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8358,11 +8385,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8380,11 +8407,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8402,11 +8429,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8424,11 +8451,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8446,11 +8473,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8468,11 +8495,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8490,11 +8517,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8512,11 +8539,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -8534,11 +8561,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -8556,11 +8583,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -8578,11 +8605,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -8600,11 +8627,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -8622,11 +8649,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -8644,11 +8671,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -8666,11 +8693,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -8688,11 +8715,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -8710,11 +8737,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -8732,11 +8759,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -8754,11 +8781,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -8776,11 +8803,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -8798,11 +8825,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -8820,11 +8847,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -8842,11 +8869,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -8864,11 +8891,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -8886,11 +8913,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -8908,11 +8935,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -8930,11 +8957,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -8952,11 +8979,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -8974,11 +9001,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -8996,11 +9023,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9018,11 +9045,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9040,11 +9067,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9062,11 +9089,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9084,11 +9111,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9106,11 +9133,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9128,11 +9155,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9150,11 +9177,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9172,11 +9199,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9194,11 +9221,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9216,11 +9243,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9238,11 +9265,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9260,11 +9287,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9282,11 +9309,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9304,11 +9331,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9326,11 +9353,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9348,11 +9375,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9370,11 +9397,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9392,11 +9419,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9414,11 +9441,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9436,11 +9463,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9458,11 +9485,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9480,11 +9507,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -9502,11 +9529,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -9524,11 +9551,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -9546,11 +9573,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -9568,11 +9595,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -9590,11 +9617,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -9612,11 +9639,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="18">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="17">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="19">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -9634,11 +9661,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -9656,11 +9683,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -9678,11 +9705,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -9700,11 +9727,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -9722,11 +9749,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -9744,11 +9771,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -9766,11 +9793,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -9788,11 +9815,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -9810,11 +9837,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -9832,11 +9859,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -9854,11 +9881,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF91D62A-F042-4CC6-BBE8-A277CF8B7EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB1284C-AAF8-4454-99A6-AA0F81900C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1303,7 +1303,7 @@
         <v>90</v>
       </c>
       <c r="E12" s="14">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="F12" s="14">
         <v>350</v>
@@ -1316,11 +1316,11 @@
       </c>
       <c r="I12" s="15">
         <f t="shared" ref="I12" si="6">IF(SUM(B12:F12,H12)=0,"",SUM(B12:F12,H12))</f>
-        <v>1105</v>
+        <v>1135</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" ref="J12" si="7">IF(I12="","",1440-I12)</f>
-        <v>335</v>
+        <v>305</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>49</v>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB1284C-AAF8-4454-99A6-AA0F81900C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9A83AD-CBB8-48A3-8993-C2377289F551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>Today, I worked on DSA Java programs and MySQL.</t>
+  </si>
+  <si>
+    <t>Today, I worked on DSA programs.</t>
   </si>
 </sst>
 </file>
@@ -1335,27 +1338,51 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="12"/>
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B13" s="14">
+        <v>450</v>
+      </c>
+      <c r="C13" s="14">
+        <v>20</v>
+      </c>
+      <c r="D13" s="14">
+        <v>60</v>
+      </c>
+      <c r="E13" s="14">
+        <v>120</v>
+      </c>
+      <c r="F13" s="14">
+        <v>200</v>
+      </c>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14">
+        <v>60</v>
+      </c>
+      <c r="I13" s="15">
+        <f t="shared" ref="I13" si="8">IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
+        <v>910</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" ref="J13" si="9">IF(I13="","",1440-I13)</f>
+        <v>530</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
@@ -2599,11 +2626,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="8">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="10">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="9">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="11">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -2621,11 +2648,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -2643,11 +2670,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -2665,11 +2692,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -2687,11 +2714,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -2709,11 +2736,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -2731,11 +2758,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -2753,11 +2780,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -2775,11 +2802,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -2797,11 +2824,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -2819,11 +2846,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -2841,11 +2868,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -2863,11 +2890,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -2885,11 +2912,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -2907,11 +2934,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -2929,11 +2956,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -2951,11 +2978,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -2973,11 +3000,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -2995,11 +3022,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3017,11 +3044,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3039,11 +3066,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3061,11 +3088,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3083,11 +3110,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3105,11 +3132,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3127,11 +3154,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3149,11 +3176,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3171,11 +3198,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3193,11 +3220,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3215,11 +3242,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3237,11 +3264,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3259,11 +3286,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3281,11 +3308,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3303,11 +3330,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3325,11 +3352,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3347,11 +3374,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3369,11 +3396,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3391,11 +3418,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3413,11 +3440,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3435,11 +3462,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3457,11 +3484,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3479,11 +3506,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3501,11 +3528,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3523,11 +3550,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3545,11 +3572,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3567,11 +3594,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3589,11 +3616,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3611,11 +3638,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -3633,11 +3660,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -3655,11 +3682,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -3677,11 +3704,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -3699,11 +3726,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -3721,11 +3748,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -3743,11 +3770,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -3765,11 +3792,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -3787,11 +3814,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -3809,11 +3836,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -3831,11 +3858,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -3853,11 +3880,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -3875,11 +3902,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -3897,11 +3924,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -3919,11 +3946,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -3941,11 +3968,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -3963,11 +3990,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -3985,11 +4012,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4007,11 +4034,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="10">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="12">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="11">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="13">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4029,11 +4056,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4051,11 +4078,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4073,11 +4100,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4095,11 +4122,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4117,11 +4144,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4139,11 +4166,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4161,11 +4188,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4183,11 +4210,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4205,11 +4232,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4227,11 +4254,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4249,11 +4276,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4271,11 +4298,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4293,11 +4320,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4315,11 +4342,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4337,11 +4364,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4359,11 +4386,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4381,11 +4408,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4403,11 +4430,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4425,11 +4452,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4447,11 +4474,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4469,11 +4496,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4491,11 +4518,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4513,11 +4540,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4535,11 +4562,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -4557,11 +4584,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -4579,11 +4606,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -4601,11 +4628,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -4623,11 +4650,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -4645,11 +4672,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -4667,11 +4694,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -4689,11 +4716,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -4711,11 +4738,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -4733,11 +4760,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -4755,11 +4782,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -4777,11 +4804,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -4799,11 +4826,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -4821,11 +4848,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -4843,11 +4870,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -4865,11 +4892,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -4887,11 +4914,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -4909,11 +4936,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -4931,11 +4958,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -4953,11 +4980,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -4975,11 +5002,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -4997,11 +5024,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5019,11 +5046,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5041,11 +5068,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5063,11 +5090,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5085,11 +5112,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5107,11 +5134,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5129,11 +5156,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5151,11 +5178,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5173,11 +5200,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5195,11 +5222,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5217,11 +5244,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5239,11 +5266,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5261,11 +5288,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5283,11 +5310,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5305,11 +5332,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5327,11 +5354,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5349,11 +5376,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5371,11 +5398,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5393,11 +5420,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5415,11 +5442,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="12">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="14">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="13">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="15">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5437,11 +5464,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5459,11 +5486,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5481,11 +5508,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5503,11 +5530,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5525,11 +5552,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -5547,11 +5574,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -5569,11 +5596,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -5591,11 +5618,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -5613,11 +5640,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -5635,11 +5662,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -5657,11 +5684,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -5679,11 +5706,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -5701,11 +5728,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -5723,11 +5750,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -5745,11 +5772,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -5767,11 +5794,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -5789,11 +5816,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -5811,11 +5838,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -5833,11 +5860,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -5855,11 +5882,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -5877,11 +5904,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -5899,11 +5926,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -5921,11 +5948,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -5943,11 +5970,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -5965,11 +5992,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -5987,11 +6014,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6009,11 +6036,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6031,11 +6058,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6053,11 +6080,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6075,11 +6102,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6097,11 +6124,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6119,11 +6146,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6141,11 +6168,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6163,11 +6190,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6185,11 +6212,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6207,11 +6234,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6229,11 +6256,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6251,11 +6278,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6273,11 +6300,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6295,11 +6322,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6317,11 +6344,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6339,11 +6366,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6361,11 +6388,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6383,11 +6410,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6405,11 +6432,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6427,11 +6454,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6449,11 +6476,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6471,11 +6498,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6493,11 +6520,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6515,11 +6542,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6537,11 +6564,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -6559,11 +6586,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -6581,11 +6608,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -6603,11 +6630,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -6625,11 +6652,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -6647,11 +6674,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -6669,11 +6696,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -6691,11 +6718,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -6713,11 +6740,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -6735,11 +6762,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -6757,11 +6784,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -6779,11 +6806,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -6801,11 +6828,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -6823,11 +6850,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="14">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="16">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="15">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="17">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -6845,11 +6872,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -6867,11 +6894,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -6889,11 +6916,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -6911,11 +6938,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -6933,11 +6960,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -6955,11 +6982,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -6977,11 +7004,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -6999,11 +7026,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7021,11 +7048,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7043,11 +7070,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7065,11 +7092,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7087,11 +7114,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7109,11 +7136,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7131,11 +7158,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7153,11 +7180,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7175,11 +7202,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7197,11 +7224,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7219,11 +7246,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7241,11 +7268,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7263,11 +7290,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7285,11 +7312,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7307,11 +7334,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7329,11 +7356,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7351,11 +7378,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7373,11 +7400,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7395,11 +7422,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7417,11 +7444,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7439,11 +7466,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7461,11 +7488,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7483,11 +7510,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7505,11 +7532,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7527,11 +7554,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -7549,11 +7576,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -7571,11 +7598,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -7593,11 +7620,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -7615,11 +7642,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -7637,11 +7664,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -7659,11 +7686,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -7681,11 +7708,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -7703,11 +7730,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -7725,11 +7752,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -7747,11 +7774,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -7769,11 +7796,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -7791,11 +7818,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -7813,11 +7840,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -7835,11 +7862,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -7857,11 +7884,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -7879,11 +7906,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -7901,11 +7928,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -7923,11 +7950,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -7945,11 +7972,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -7967,11 +7994,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -7989,11 +8016,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8011,11 +8038,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8033,11 +8060,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8055,11 +8082,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8077,11 +8104,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8099,11 +8126,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8121,11 +8148,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8143,11 +8170,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8165,11 +8192,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8187,11 +8214,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8209,11 +8236,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8231,11 +8258,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="16">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="18">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="17">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="19">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8253,11 +8280,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8275,11 +8302,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8297,11 +8324,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8319,11 +8346,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8341,11 +8368,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8363,11 +8390,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8385,11 +8412,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8407,11 +8434,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8429,11 +8456,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8451,11 +8478,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8473,11 +8500,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8495,11 +8522,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8517,11 +8544,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8539,11 +8566,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -8561,11 +8588,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -8583,11 +8610,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -8605,11 +8632,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -8627,11 +8654,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -8649,11 +8676,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -8671,11 +8698,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -8693,11 +8720,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -8715,11 +8742,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -8737,11 +8764,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -8759,11 +8786,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -8781,11 +8808,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -8803,11 +8830,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -8825,11 +8852,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -8847,11 +8874,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -8869,11 +8896,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -8891,11 +8918,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -8913,11 +8940,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -8935,11 +8962,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -8957,11 +8984,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -8979,11 +9006,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9001,11 +9028,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9023,11 +9050,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9045,11 +9072,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9067,11 +9094,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9089,11 +9116,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9111,11 +9138,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9133,11 +9160,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9155,11 +9182,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9177,11 +9204,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9199,11 +9226,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9221,11 +9248,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9243,11 +9270,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9265,11 +9292,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9287,11 +9314,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9309,11 +9336,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9331,11 +9358,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9353,11 +9380,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9375,11 +9402,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9397,11 +9424,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9419,11 +9446,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9441,11 +9468,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9463,11 +9490,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9485,11 +9512,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9507,11 +9534,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -9529,11 +9556,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -9551,11 +9578,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -9573,11 +9600,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -9595,11 +9622,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -9617,11 +9644,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -9639,11 +9666,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="18">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="20">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="19">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="21">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -9661,11 +9688,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -9683,11 +9710,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -9705,11 +9732,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -9727,11 +9754,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -9749,11 +9776,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -9771,11 +9798,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -9793,11 +9820,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -9815,11 +9842,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -9837,11 +9864,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -9859,11 +9886,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -9881,11 +9908,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9A83AD-CBB8-48A3-8993-C2377289F551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B8600D-9BF6-4553-98C2-E82103E1723E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>Today, I worked on DSA programs.</t>
+  </si>
+  <si>
+    <t>Today, I worked on DSA and Python programs.</t>
   </si>
 </sst>
 </file>
@@ -1384,27 +1387,51 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="12"/>
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B14" s="14">
+        <v>450</v>
+      </c>
+      <c r="C14" s="14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
+        <v>60</v>
+      </c>
+      <c r="E14" s="14">
+        <v>120</v>
+      </c>
+      <c r="F14" s="14">
+        <v>400</v>
+      </c>
+      <c r="G14" s="14">
+        <v>8</v>
+      </c>
+      <c r="H14" s="14">
+        <v>60</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" ref="I14" si="10">IF(SUM(B14:F14,H14)=0,"",SUM(B14:F14,H14))</f>
+        <v>1090</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" ref="J14" si="11">IF(I14="","",1440-I14)</f>
+        <v>350</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
@@ -2626,11 +2653,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="10">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="12">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="11">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="13">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -2648,11 +2675,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -2670,11 +2697,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -2692,11 +2719,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -2714,11 +2741,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -2736,11 +2763,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -2758,11 +2785,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -2780,11 +2807,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -2802,11 +2829,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -2824,11 +2851,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -2846,11 +2873,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -2868,11 +2895,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -2890,11 +2917,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -2912,11 +2939,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -2934,11 +2961,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -2956,11 +2983,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -2978,11 +3005,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3000,11 +3027,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3022,11 +3049,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3044,11 +3071,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3066,11 +3093,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3088,11 +3115,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3110,11 +3137,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3132,11 +3159,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3154,11 +3181,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3176,11 +3203,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3198,11 +3225,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3220,11 +3247,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3242,11 +3269,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3264,11 +3291,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3286,11 +3313,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3308,11 +3335,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3330,11 +3357,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3352,11 +3379,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3374,11 +3401,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3396,11 +3423,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3418,11 +3445,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3440,11 +3467,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3462,11 +3489,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3484,11 +3511,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3506,11 +3533,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3528,11 +3555,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3550,11 +3577,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3572,11 +3599,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3594,11 +3621,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3616,11 +3643,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3638,11 +3665,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -3660,11 +3687,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -3682,11 +3709,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -3704,11 +3731,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -3726,11 +3753,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -3748,11 +3775,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -3770,11 +3797,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -3792,11 +3819,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -3814,11 +3841,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -3836,11 +3863,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -3858,11 +3885,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -3880,11 +3907,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -3902,11 +3929,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -3924,11 +3951,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -3946,11 +3973,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -3968,11 +3995,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -3990,11 +4017,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4012,11 +4039,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4034,11 +4061,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="12">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="14">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="13">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="15">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4056,11 +4083,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4078,11 +4105,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4100,11 +4127,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4122,11 +4149,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4144,11 +4171,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4166,11 +4193,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4188,11 +4215,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4210,11 +4237,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4232,11 +4259,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4254,11 +4281,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4276,11 +4303,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4298,11 +4325,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4320,11 +4347,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4342,11 +4369,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4364,11 +4391,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4386,11 +4413,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4408,11 +4435,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4430,11 +4457,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4452,11 +4479,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4474,11 +4501,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4496,11 +4523,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4518,11 +4545,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4540,11 +4567,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4562,11 +4589,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -4584,11 +4611,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -4606,11 +4633,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -4628,11 +4655,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -4650,11 +4677,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -4672,11 +4699,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -4694,11 +4721,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -4716,11 +4743,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -4738,11 +4765,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -4760,11 +4787,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -4782,11 +4809,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -4804,11 +4831,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -4826,11 +4853,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -4848,11 +4875,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -4870,11 +4897,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -4892,11 +4919,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -4914,11 +4941,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -4936,11 +4963,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -4958,11 +4985,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -4980,11 +5007,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5002,11 +5029,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5024,11 +5051,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5046,11 +5073,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5068,11 +5095,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5090,11 +5117,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5112,11 +5139,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5134,11 +5161,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5156,11 +5183,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5178,11 +5205,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5200,11 +5227,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5222,11 +5249,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5244,11 +5271,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5266,11 +5293,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5288,11 +5315,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5310,11 +5337,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5332,11 +5359,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5354,11 +5381,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5376,11 +5403,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5398,11 +5425,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5420,11 +5447,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5442,11 +5469,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="14">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="16">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="15">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="17">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5464,11 +5491,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5486,11 +5513,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5508,11 +5535,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5530,11 +5557,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5552,11 +5579,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -5574,11 +5601,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -5596,11 +5623,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -5618,11 +5645,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -5640,11 +5667,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -5662,11 +5689,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -5684,11 +5711,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -5706,11 +5733,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -5728,11 +5755,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -5750,11 +5777,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -5772,11 +5799,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -5794,11 +5821,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -5816,11 +5843,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -5838,11 +5865,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -5860,11 +5887,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -5882,11 +5909,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -5904,11 +5931,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -5926,11 +5953,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -5948,11 +5975,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -5970,11 +5997,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -5992,11 +6019,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6014,11 +6041,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6036,11 +6063,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6058,11 +6085,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6080,11 +6107,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6102,11 +6129,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6124,11 +6151,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6146,11 +6173,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6168,11 +6195,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6190,11 +6217,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6212,11 +6239,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6234,11 +6261,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6256,11 +6283,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6278,11 +6305,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6300,11 +6327,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6322,11 +6349,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6344,11 +6371,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6366,11 +6393,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6388,11 +6415,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6410,11 +6437,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6432,11 +6459,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6454,11 +6481,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6476,11 +6503,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6498,11 +6525,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6520,11 +6547,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6542,11 +6569,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6564,11 +6591,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -6586,11 +6613,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -6608,11 +6635,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -6630,11 +6657,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -6652,11 +6679,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -6674,11 +6701,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -6696,11 +6723,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -6718,11 +6745,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -6740,11 +6767,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -6762,11 +6789,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -6784,11 +6811,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -6806,11 +6833,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -6828,11 +6855,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -6850,11 +6877,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="16">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="18">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="17">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="19">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -6872,11 +6899,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -6894,11 +6921,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -6916,11 +6943,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -6938,11 +6965,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -6960,11 +6987,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -6982,11 +7009,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7004,11 +7031,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7026,11 +7053,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7048,11 +7075,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7070,11 +7097,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7092,11 +7119,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7114,11 +7141,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7136,11 +7163,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7158,11 +7185,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7180,11 +7207,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7202,11 +7229,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7224,11 +7251,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7246,11 +7273,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7268,11 +7295,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7290,11 +7317,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7312,11 +7339,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7334,11 +7361,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7356,11 +7383,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7378,11 +7405,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7400,11 +7427,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7422,11 +7449,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7444,11 +7471,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7466,11 +7493,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7488,11 +7515,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7510,11 +7537,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7532,11 +7559,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7554,11 +7581,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -7576,11 +7603,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -7598,11 +7625,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -7620,11 +7647,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -7642,11 +7669,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -7664,11 +7691,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -7686,11 +7713,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -7708,11 +7735,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -7730,11 +7757,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -7752,11 +7779,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -7774,11 +7801,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -7796,11 +7823,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -7818,11 +7845,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -7840,11 +7867,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -7862,11 +7889,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -7884,11 +7911,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -7906,11 +7933,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -7928,11 +7955,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -7950,11 +7977,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -7972,11 +7999,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -7994,11 +8021,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8016,11 +8043,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8038,11 +8065,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8060,11 +8087,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8082,11 +8109,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8104,11 +8131,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8126,11 +8153,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8148,11 +8175,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8170,11 +8197,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8192,11 +8219,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8214,11 +8241,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8236,11 +8263,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8258,11 +8285,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="18">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="20">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="19">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="21">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8280,11 +8307,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8302,11 +8329,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8324,11 +8351,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8346,11 +8373,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8368,11 +8395,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8390,11 +8417,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8412,11 +8439,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8434,11 +8461,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8456,11 +8483,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8478,11 +8505,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8500,11 +8527,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8522,11 +8549,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8544,11 +8571,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8566,11 +8593,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -8588,11 +8615,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -8610,11 +8637,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -8632,11 +8659,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -8654,11 +8681,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -8676,11 +8703,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -8698,11 +8725,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -8720,11 +8747,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -8742,11 +8769,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -8764,11 +8791,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -8786,11 +8813,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -8808,11 +8835,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -8830,11 +8857,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -8852,11 +8879,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -8874,11 +8901,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -8896,11 +8923,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -8918,11 +8945,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -8940,11 +8967,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -8962,11 +8989,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -8984,11 +9011,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9006,11 +9033,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9028,11 +9055,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9050,11 +9077,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9072,11 +9099,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9094,11 +9121,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9116,11 +9143,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9138,11 +9165,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9160,11 +9187,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9182,11 +9209,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9204,11 +9231,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9226,11 +9253,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9248,11 +9275,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9270,11 +9297,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9292,11 +9319,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9314,11 +9341,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9336,11 +9363,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9358,11 +9385,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9380,11 +9407,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9402,11 +9429,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9424,11 +9451,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9446,11 +9473,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9468,11 +9495,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9490,11 +9517,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9512,11 +9539,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9534,11 +9561,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -9556,11 +9583,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -9578,11 +9605,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -9600,11 +9627,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -9622,11 +9649,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -9644,11 +9671,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -9666,11 +9693,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="20">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="22">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="21">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="23">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -9688,11 +9715,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -9710,11 +9737,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -9732,11 +9759,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -9754,11 +9781,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -9776,11 +9803,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -9798,11 +9825,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -9820,11 +9847,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -9842,11 +9869,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -9864,11 +9891,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -9886,11 +9913,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -9908,11 +9935,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B8600D-9BF6-4553-98C2-E82103E1723E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C4C642-E7D6-43E8-9589-99B17F1B77E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>Today, I worked on DSA and Python programs.</t>
+  </si>
+  <si>
+    <t>Today, I worked on DSA and College Subjects.</t>
   </si>
 </sst>
 </file>
@@ -1421,105 +1424,201 @@
         <v>350</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N14" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10" t="str">
-        <f>IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="12"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="12"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="12"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="12"/>
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B15" s="14">
+        <v>480</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>60</v>
+      </c>
+      <c r="E15" s="14">
+        <v>180</v>
+      </c>
+      <c r="F15" s="14">
+        <v>400</v>
+      </c>
+      <c r="G15" s="14">
+        <v>8</v>
+      </c>
+      <c r="H15" s="14">
+        <v>60</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" ref="I15:I18" si="12">IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
+        <v>1180</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" ref="J15:J18" si="13">IF(I15="","",1440-I15)</f>
+        <v>260</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B16" s="14">
+        <v>450</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>70</v>
+      </c>
+      <c r="E16" s="14">
+        <v>120</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>60</v>
+      </c>
+      <c r="I16" s="15">
+        <f t="shared" si="12"/>
+        <v>700</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" si="13"/>
+        <v>740</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B17" s="14">
+        <v>480</v>
+      </c>
+      <c r="C17" s="14">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
+        <v>60</v>
+      </c>
+      <c r="E17" s="14">
+        <v>120</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>60</v>
+      </c>
+      <c r="I17" s="15">
+        <f t="shared" si="12"/>
+        <v>740</v>
+      </c>
+      <c r="J17" s="15">
+        <f t="shared" si="13"/>
+        <v>700</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B18" s="14">
+        <v>480</v>
+      </c>
+      <c r="C18" s="14">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>60</v>
+      </c>
+      <c r="E18" s="14">
+        <v>150</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>60</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" si="12"/>
+        <v>770</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" si="13"/>
+        <v>670</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
@@ -2653,11 +2752,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="12">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="14">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="13">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="15">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -2675,11 +2774,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -2697,11 +2796,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -2719,11 +2818,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -2741,11 +2840,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -2763,11 +2862,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -2785,11 +2884,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -2807,11 +2906,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -2829,11 +2928,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -2851,11 +2950,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -2873,11 +2972,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -2895,11 +2994,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -2917,11 +3016,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -2939,11 +3038,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -2961,11 +3060,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -2983,11 +3082,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3005,11 +3104,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3027,11 +3126,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3049,11 +3148,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3071,11 +3170,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3093,11 +3192,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3115,11 +3214,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3137,11 +3236,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3159,11 +3258,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3181,11 +3280,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3203,11 +3302,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3225,11 +3324,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3247,11 +3346,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3269,11 +3368,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3291,11 +3390,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3313,11 +3412,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3335,11 +3434,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3357,11 +3456,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3379,11 +3478,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3401,11 +3500,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3423,11 +3522,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3445,11 +3544,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3467,11 +3566,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3489,11 +3588,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3511,11 +3610,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3533,11 +3632,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3555,11 +3654,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3577,11 +3676,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3599,11 +3698,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3621,11 +3720,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3643,11 +3742,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3665,11 +3764,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -3687,11 +3786,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -3709,11 +3808,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -3731,11 +3830,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -3753,11 +3852,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -3775,11 +3874,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -3797,11 +3896,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -3819,11 +3918,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -3841,11 +3940,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -3863,11 +3962,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -3885,11 +3984,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -3907,11 +4006,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -3929,11 +4028,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -3951,11 +4050,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -3973,11 +4072,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -3995,11 +4094,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4017,11 +4116,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4039,11 +4138,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4061,11 +4160,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="14">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="16">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="15">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="17">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4083,11 +4182,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4105,11 +4204,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4127,11 +4226,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4149,11 +4248,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4171,11 +4270,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4193,11 +4292,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4215,11 +4314,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4237,11 +4336,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4259,11 +4358,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4281,11 +4380,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4303,11 +4402,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4325,11 +4424,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4347,11 +4446,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4369,11 +4468,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4391,11 +4490,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4413,11 +4512,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4435,11 +4534,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4457,11 +4556,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4479,11 +4578,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4501,11 +4600,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4523,11 +4622,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4545,11 +4644,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4567,11 +4666,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4589,11 +4688,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -4611,11 +4710,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -4633,11 +4732,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -4655,11 +4754,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -4677,11 +4776,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -4699,11 +4798,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -4721,11 +4820,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -4743,11 +4842,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -4765,11 +4864,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -4787,11 +4886,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -4809,11 +4908,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -4831,11 +4930,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -4853,11 +4952,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -4875,11 +4974,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -4897,11 +4996,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -4919,11 +5018,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -4941,11 +5040,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -4963,11 +5062,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -4985,11 +5084,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5007,11 +5106,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5029,11 +5128,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5051,11 +5150,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5073,11 +5172,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5095,11 +5194,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5117,11 +5216,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5139,11 +5238,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5161,11 +5260,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5183,11 +5282,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5205,11 +5304,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5227,11 +5326,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5249,11 +5348,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5271,11 +5370,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5293,11 +5392,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5315,11 +5414,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5337,11 +5436,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5359,11 +5458,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5381,11 +5480,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5403,11 +5502,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5425,11 +5524,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5447,11 +5546,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5469,11 +5568,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="16">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="18">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="17">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="19">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5491,11 +5590,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5513,11 +5612,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5535,11 +5634,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5557,11 +5656,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5579,11 +5678,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -5601,11 +5700,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -5623,11 +5722,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -5645,11 +5744,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -5667,11 +5766,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -5689,11 +5788,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -5711,11 +5810,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -5733,11 +5832,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -5755,11 +5854,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -5777,11 +5876,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -5799,11 +5898,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -5821,11 +5920,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -5843,11 +5942,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -5865,11 +5964,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -5887,11 +5986,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -5909,11 +6008,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -5931,11 +6030,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -5953,11 +6052,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -5975,11 +6074,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -5997,11 +6096,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6019,11 +6118,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6041,11 +6140,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6063,11 +6162,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6085,11 +6184,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6107,11 +6206,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6129,11 +6228,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6151,11 +6250,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6173,11 +6272,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6195,11 +6294,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6217,11 +6316,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6239,11 +6338,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6261,11 +6360,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6283,11 +6382,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6305,11 +6404,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6327,11 +6426,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6349,11 +6448,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6371,11 +6470,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6393,11 +6492,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6415,11 +6514,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6437,11 +6536,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6459,11 +6558,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6481,11 +6580,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6503,11 +6602,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6525,11 +6624,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6547,11 +6646,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6569,11 +6668,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6591,11 +6690,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -6613,11 +6712,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -6635,11 +6734,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -6657,11 +6756,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -6679,11 +6778,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -6701,11 +6800,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -6723,11 +6822,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -6745,11 +6844,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -6767,11 +6866,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -6789,11 +6888,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -6811,11 +6910,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -6833,11 +6932,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -6855,11 +6954,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -6877,11 +6976,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="18">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="20">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="19">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="21">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -6899,11 +6998,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -6921,11 +7020,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -6943,11 +7042,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -6965,11 +7064,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -6987,11 +7086,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7009,11 +7108,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7031,11 +7130,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7053,11 +7152,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7075,11 +7174,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7097,11 +7196,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7119,11 +7218,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7141,11 +7240,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7163,11 +7262,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7185,11 +7284,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7207,11 +7306,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7229,11 +7328,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7251,11 +7350,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7273,11 +7372,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7295,11 +7394,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7317,11 +7416,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7339,11 +7438,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7361,11 +7460,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7383,11 +7482,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7405,11 +7504,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7427,11 +7526,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7449,11 +7548,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7471,11 +7570,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7493,11 +7592,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7515,11 +7614,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7537,11 +7636,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7559,11 +7658,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7581,11 +7680,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -7603,11 +7702,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -7625,11 +7724,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -7647,11 +7746,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -7669,11 +7768,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -7691,11 +7790,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -7713,11 +7812,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -7735,11 +7834,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -7757,11 +7856,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -7779,11 +7878,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -7801,11 +7900,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -7823,11 +7922,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -7845,11 +7944,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -7867,11 +7966,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -7889,11 +7988,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -7911,11 +8010,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -7933,11 +8032,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -7955,11 +8054,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -7977,11 +8076,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -7999,11 +8098,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8021,11 +8120,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8043,11 +8142,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8065,11 +8164,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8087,11 +8186,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8109,11 +8208,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8131,11 +8230,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8153,11 +8252,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8175,11 +8274,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8197,11 +8296,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8219,11 +8318,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8241,11 +8340,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8263,11 +8362,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8285,11 +8384,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="20">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="22">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="21">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="23">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8307,11 +8406,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8329,11 +8428,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8351,11 +8450,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8373,11 +8472,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8395,11 +8494,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8417,11 +8516,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8439,11 +8538,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8461,11 +8560,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8483,11 +8582,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8505,11 +8604,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8527,11 +8626,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8549,11 +8648,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8571,11 +8670,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8593,11 +8692,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -8615,11 +8714,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -8637,11 +8736,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -8659,11 +8758,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -8681,11 +8780,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -8703,11 +8802,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -8725,11 +8824,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -8747,11 +8846,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -8769,11 +8868,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -8791,11 +8890,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -8813,11 +8912,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -8835,11 +8934,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -8857,11 +8956,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -8879,11 +8978,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -8901,11 +9000,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -8923,11 +9022,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -8945,11 +9044,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -8967,11 +9066,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -8989,11 +9088,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9011,11 +9110,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9033,11 +9132,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9055,11 +9154,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9077,11 +9176,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9099,11 +9198,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9121,11 +9220,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9143,11 +9242,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9165,11 +9264,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9187,11 +9286,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9209,11 +9308,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9231,11 +9330,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9253,11 +9352,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9275,11 +9374,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9297,11 +9396,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9319,11 +9418,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9341,11 +9440,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9363,11 +9462,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9385,11 +9484,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9407,11 +9506,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9429,11 +9528,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9451,11 +9550,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9473,11 +9572,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9495,11 +9594,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9517,11 +9616,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9539,11 +9638,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9561,11 +9660,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -9583,11 +9682,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -9605,11 +9704,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -9627,11 +9726,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -9649,11 +9748,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -9671,11 +9770,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -9693,11 +9792,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="22">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="24">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="23">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="25">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -9715,11 +9814,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -9737,11 +9836,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -9759,11 +9858,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -9781,11 +9880,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -9803,11 +9902,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -9825,11 +9924,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -9847,11 +9946,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -9869,11 +9968,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -9891,11 +9990,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -9913,11 +10012,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -9935,11 +10034,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C4C642-E7D6-43E8-9589-99B17F1B77E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340D8475-7078-4A92-B6B8-0359550EE640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>Today, I worked on DSA and College Subjects.</t>
+  </si>
+  <si>
+    <t>Today, I worked on DSA, SQL Queries and College Subjects.</t>
   </si>
 </sst>
 </file>
@@ -1620,27 +1623,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="12"/>
+    <row r="19" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B19" s="14">
+        <v>450</v>
+      </c>
+      <c r="C19" s="14">
+        <v>20</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>100</v>
+      </c>
+      <c r="F19" s="14">
+        <v>350</v>
+      </c>
+      <c r="G19" s="14">
+        <v>7</v>
+      </c>
+      <c r="H19" s="14">
+        <v>60</v>
+      </c>
+      <c r="I19" s="15">
+        <f t="shared" ref="I19" si="14">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
+        <v>1100</v>
+      </c>
+      <c r="J19" s="15">
+        <f t="shared" ref="J19" si="15">IF(I19="","",1440-I19)</f>
+        <v>340</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
@@ -2752,11 +2779,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="14">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="16">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="15">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="17">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -2774,11 +2801,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -2796,11 +2823,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -2818,11 +2845,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -2840,11 +2867,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -2862,11 +2889,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -2884,11 +2911,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -2906,11 +2933,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -2928,11 +2955,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -2950,11 +2977,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -2972,11 +2999,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -2994,11 +3021,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3016,11 +3043,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3038,11 +3065,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3060,11 +3087,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3082,11 +3109,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3104,11 +3131,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3126,11 +3153,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3148,11 +3175,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3170,11 +3197,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3192,11 +3219,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3214,11 +3241,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3236,11 +3263,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3258,11 +3285,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3280,11 +3307,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3302,11 +3329,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3324,11 +3351,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3346,11 +3373,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3368,11 +3395,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3390,11 +3417,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3412,11 +3439,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3434,11 +3461,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3456,11 +3483,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3478,11 +3505,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3500,11 +3527,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3522,11 +3549,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3544,11 +3571,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3566,11 +3593,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3588,11 +3615,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3610,11 +3637,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3632,11 +3659,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3654,11 +3681,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3676,11 +3703,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3698,11 +3725,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3720,11 +3747,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3742,11 +3769,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3764,11 +3791,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -3786,11 +3813,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -3808,11 +3835,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -3830,11 +3857,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -3852,11 +3879,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -3874,11 +3901,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -3896,11 +3923,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -3918,11 +3945,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -3940,11 +3967,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -3962,11 +3989,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -3984,11 +4011,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4006,11 +4033,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4028,11 +4055,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4050,11 +4077,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4072,11 +4099,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4094,11 +4121,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4116,11 +4143,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4138,11 +4165,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4160,11 +4187,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="16">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="18">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="17">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="19">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4182,11 +4209,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4204,11 +4231,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4226,11 +4253,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4248,11 +4275,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4270,11 +4297,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4292,11 +4319,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4314,11 +4341,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4336,11 +4363,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4358,11 +4385,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4380,11 +4407,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4402,11 +4429,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4424,11 +4451,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4446,11 +4473,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4468,11 +4495,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4490,11 +4517,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4512,11 +4539,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4534,11 +4561,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4556,11 +4583,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4578,11 +4605,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4600,11 +4627,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4622,11 +4649,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4644,11 +4671,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4666,11 +4693,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4688,11 +4715,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -4710,11 +4737,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -4732,11 +4759,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -4754,11 +4781,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -4776,11 +4803,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -4798,11 +4825,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -4820,11 +4847,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -4842,11 +4869,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -4864,11 +4891,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -4886,11 +4913,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -4908,11 +4935,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -4930,11 +4957,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -4952,11 +4979,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -4974,11 +5001,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -4996,11 +5023,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5018,11 +5045,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5040,11 +5067,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5062,11 +5089,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5084,11 +5111,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5106,11 +5133,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5128,11 +5155,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5150,11 +5177,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5172,11 +5199,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5194,11 +5221,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5216,11 +5243,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5238,11 +5265,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5260,11 +5287,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5282,11 +5309,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5304,11 +5331,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5326,11 +5353,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5348,11 +5375,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5370,11 +5397,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5392,11 +5419,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5414,11 +5441,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5436,11 +5463,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5458,11 +5485,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5480,11 +5507,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5502,11 +5529,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5524,11 +5551,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5546,11 +5573,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5568,11 +5595,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="18">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="20">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="19">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="21">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5590,11 +5617,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5612,11 +5639,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5634,11 +5661,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5656,11 +5683,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5678,11 +5705,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -5700,11 +5727,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -5722,11 +5749,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -5744,11 +5771,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -5766,11 +5793,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -5788,11 +5815,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -5810,11 +5837,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -5832,11 +5859,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -5854,11 +5881,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -5876,11 +5903,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -5898,11 +5925,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -5920,11 +5947,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -5942,11 +5969,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -5964,11 +5991,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -5986,11 +6013,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6008,11 +6035,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6030,11 +6057,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6052,11 +6079,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6074,11 +6101,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6096,11 +6123,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6118,11 +6145,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6140,11 +6167,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6162,11 +6189,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6184,11 +6211,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6206,11 +6233,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6228,11 +6255,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6250,11 +6277,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6272,11 +6299,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6294,11 +6321,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6316,11 +6343,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6338,11 +6365,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6360,11 +6387,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6382,11 +6409,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6404,11 +6431,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6426,11 +6453,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6448,11 +6475,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6470,11 +6497,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6492,11 +6519,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6514,11 +6541,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6536,11 +6563,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6558,11 +6585,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6580,11 +6607,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6602,11 +6629,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6624,11 +6651,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6646,11 +6673,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6668,11 +6695,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6690,11 +6717,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -6712,11 +6739,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -6734,11 +6761,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -6756,11 +6783,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -6778,11 +6805,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -6800,11 +6827,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -6822,11 +6849,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -6844,11 +6871,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -6866,11 +6893,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -6888,11 +6915,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -6910,11 +6937,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -6932,11 +6959,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -6954,11 +6981,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -6976,11 +7003,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="20">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="22">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="21">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="23">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -6998,11 +7025,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7020,11 +7047,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7042,11 +7069,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7064,11 +7091,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7086,11 +7113,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7108,11 +7135,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7130,11 +7157,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7152,11 +7179,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7174,11 +7201,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7196,11 +7223,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7218,11 +7245,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7240,11 +7267,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7262,11 +7289,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7284,11 +7311,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7306,11 +7333,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7328,11 +7355,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7350,11 +7377,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7372,11 +7399,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7394,11 +7421,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7416,11 +7443,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7438,11 +7465,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7460,11 +7487,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7482,11 +7509,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7504,11 +7531,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7526,11 +7553,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7548,11 +7575,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7570,11 +7597,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7592,11 +7619,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7614,11 +7641,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7636,11 +7663,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7658,11 +7685,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7680,11 +7707,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -7702,11 +7729,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -7724,11 +7751,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -7746,11 +7773,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -7768,11 +7795,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -7790,11 +7817,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -7812,11 +7839,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -7834,11 +7861,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -7856,11 +7883,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -7878,11 +7905,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -7900,11 +7927,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -7922,11 +7949,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -7944,11 +7971,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -7966,11 +7993,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -7988,11 +8015,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8010,11 +8037,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8032,11 +8059,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8054,11 +8081,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8076,11 +8103,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8098,11 +8125,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8120,11 +8147,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8142,11 +8169,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8164,11 +8191,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8186,11 +8213,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8208,11 +8235,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8230,11 +8257,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8252,11 +8279,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8274,11 +8301,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8296,11 +8323,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8318,11 +8345,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8340,11 +8367,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8362,11 +8389,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8384,11 +8411,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="22">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="24">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="23">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="25">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8406,11 +8433,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8428,11 +8455,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8450,11 +8477,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8472,11 +8499,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8494,11 +8521,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8516,11 +8543,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8538,11 +8565,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8560,11 +8587,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8582,11 +8609,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8604,11 +8631,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8626,11 +8653,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8648,11 +8675,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8670,11 +8697,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8692,11 +8719,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -8714,11 +8741,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -8736,11 +8763,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -8758,11 +8785,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -8780,11 +8807,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -8802,11 +8829,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -8824,11 +8851,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -8846,11 +8873,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -8868,11 +8895,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -8890,11 +8917,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -8912,11 +8939,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -8934,11 +8961,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -8956,11 +8983,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -8978,11 +9005,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9000,11 +9027,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9022,11 +9049,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9044,11 +9071,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9066,11 +9093,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9088,11 +9115,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9110,11 +9137,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9132,11 +9159,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9154,11 +9181,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9176,11 +9203,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9198,11 +9225,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9220,11 +9247,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9242,11 +9269,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9264,11 +9291,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9286,11 +9313,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9308,11 +9335,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9330,11 +9357,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9352,11 +9379,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9374,11 +9401,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9396,11 +9423,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9418,11 +9445,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9440,11 +9467,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9462,11 +9489,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9484,11 +9511,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9506,11 +9533,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9528,11 +9555,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9550,11 +9577,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9572,11 +9599,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9594,11 +9621,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9616,11 +9643,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9638,11 +9665,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9660,11 +9687,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -9682,11 +9709,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -9704,11 +9731,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -9726,11 +9753,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -9748,11 +9775,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -9770,11 +9797,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -9792,11 +9819,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="24">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="26">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="25">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="27">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -9814,11 +9841,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -9836,11 +9863,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -9858,11 +9885,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -9880,11 +9907,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -9902,11 +9929,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -9924,11 +9951,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -9946,11 +9973,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -9968,11 +9995,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -9990,11 +10017,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10012,11 +10039,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10034,11 +10061,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340D8475-7078-4A92-B6B8-0359550EE640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF6DD86-2D9C-4EF6-AC72-BC5F80DA99B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1669,27 +1669,51 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="12"/>
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B20" s="14">
+        <v>450</v>
+      </c>
+      <c r="C20" s="14">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>30</v>
+      </c>
+      <c r="F20" s="14">
+        <v>350</v>
+      </c>
+      <c r="G20" s="14">
+        <v>7</v>
+      </c>
+      <c r="H20" s="14">
+        <v>60</v>
+      </c>
+      <c r="I20" s="15">
+        <f t="shared" ref="I20" si="16">IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
+        <v>1030</v>
+      </c>
+      <c r="J20" s="15">
+        <f t="shared" ref="J20" si="17">IF(I20="","",1440-I20)</f>
+        <v>410</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
@@ -2779,11 +2803,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="16">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="18">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="17">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="19">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -2801,11 +2825,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -2823,11 +2847,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -2845,11 +2869,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -2867,11 +2891,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -2889,11 +2913,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -2911,11 +2935,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -2933,11 +2957,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -2955,11 +2979,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -2977,11 +3001,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -2999,11 +3023,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3021,11 +3045,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3043,11 +3067,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3065,11 +3089,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3087,11 +3111,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3109,11 +3133,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3131,11 +3155,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3153,11 +3177,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3175,11 +3199,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3197,11 +3221,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3219,11 +3243,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3241,11 +3265,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3263,11 +3287,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3285,11 +3309,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3307,11 +3331,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3329,11 +3353,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3351,11 +3375,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3373,11 +3397,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3395,11 +3419,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3417,11 +3441,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3439,11 +3463,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3461,11 +3485,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3483,11 +3507,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3505,11 +3529,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3527,11 +3551,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3549,11 +3573,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3571,11 +3595,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3593,11 +3617,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3615,11 +3639,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3637,11 +3661,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3659,11 +3683,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3681,11 +3705,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3703,11 +3727,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3725,11 +3749,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3747,11 +3771,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3769,11 +3793,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3791,11 +3815,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -3813,11 +3837,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -3835,11 +3859,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -3857,11 +3881,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -3879,11 +3903,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -3901,11 +3925,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -3923,11 +3947,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -3945,11 +3969,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -3967,11 +3991,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -3989,11 +4013,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4011,11 +4035,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4033,11 +4057,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4055,11 +4079,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4077,11 +4101,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4099,11 +4123,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4121,11 +4145,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4143,11 +4167,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4165,11 +4189,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4187,11 +4211,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="18">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="20">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="19">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="21">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4209,11 +4233,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4231,11 +4255,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4253,11 +4277,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4275,11 +4299,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4297,11 +4321,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4319,11 +4343,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4341,11 +4365,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4363,11 +4387,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4385,11 +4409,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4407,11 +4431,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4429,11 +4453,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4451,11 +4475,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4473,11 +4497,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4495,11 +4519,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4517,11 +4541,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4539,11 +4563,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4561,11 +4585,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4583,11 +4607,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4605,11 +4629,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4627,11 +4651,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4649,11 +4673,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4671,11 +4695,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4693,11 +4717,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4715,11 +4739,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -4737,11 +4761,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -4759,11 +4783,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -4781,11 +4805,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -4803,11 +4827,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -4825,11 +4849,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -4847,11 +4871,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -4869,11 +4893,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -4891,11 +4915,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -4913,11 +4937,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -4935,11 +4959,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -4957,11 +4981,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -4979,11 +5003,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5001,11 +5025,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5023,11 +5047,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5045,11 +5069,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5067,11 +5091,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5089,11 +5113,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5111,11 +5135,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5133,11 +5157,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5155,11 +5179,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5177,11 +5201,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5199,11 +5223,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5221,11 +5245,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5243,11 +5267,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5265,11 +5289,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5287,11 +5311,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5309,11 +5333,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5331,11 +5355,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5353,11 +5377,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5375,11 +5399,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5397,11 +5421,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5419,11 +5443,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5441,11 +5465,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5463,11 +5487,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5485,11 +5509,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5507,11 +5531,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5529,11 +5553,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5551,11 +5575,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5573,11 +5597,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5595,11 +5619,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="20">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="22">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="21">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="23">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5617,11 +5641,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5639,11 +5663,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5661,11 +5685,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5683,11 +5707,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5705,11 +5729,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -5727,11 +5751,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -5749,11 +5773,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -5771,11 +5795,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -5793,11 +5817,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -5815,11 +5839,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -5837,11 +5861,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -5859,11 +5883,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -5881,11 +5905,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -5903,11 +5927,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -5925,11 +5949,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -5947,11 +5971,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -5969,11 +5993,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -5991,11 +6015,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6013,11 +6037,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6035,11 +6059,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6057,11 +6081,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6079,11 +6103,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6101,11 +6125,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6123,11 +6147,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6145,11 +6169,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6167,11 +6191,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6189,11 +6213,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6211,11 +6235,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6233,11 +6257,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6255,11 +6279,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6277,11 +6301,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6299,11 +6323,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6321,11 +6345,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6343,11 +6367,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6365,11 +6389,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6387,11 +6411,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6409,11 +6433,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6431,11 +6455,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6453,11 +6477,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6475,11 +6499,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6497,11 +6521,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6519,11 +6543,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6541,11 +6565,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6563,11 +6587,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6585,11 +6609,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6607,11 +6631,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6629,11 +6653,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6651,11 +6675,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6673,11 +6697,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6695,11 +6719,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6717,11 +6741,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -6739,11 +6763,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -6761,11 +6785,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -6783,11 +6807,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -6805,11 +6829,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -6827,11 +6851,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -6849,11 +6873,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -6871,11 +6895,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -6893,11 +6917,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -6915,11 +6939,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -6937,11 +6961,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -6959,11 +6983,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -6981,11 +7005,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7003,11 +7027,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="22">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="24">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="23">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="25">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7025,11 +7049,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7047,11 +7071,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7069,11 +7093,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7091,11 +7115,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7113,11 +7137,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7135,11 +7159,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7157,11 +7181,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7179,11 +7203,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7201,11 +7225,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7223,11 +7247,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7245,11 +7269,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7267,11 +7291,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7289,11 +7313,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7311,11 +7335,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7333,11 +7357,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7355,11 +7379,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7377,11 +7401,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7399,11 +7423,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7421,11 +7445,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7443,11 +7467,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7465,11 +7489,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7487,11 +7511,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7509,11 +7533,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7531,11 +7555,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7553,11 +7577,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7575,11 +7599,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7597,11 +7621,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7619,11 +7643,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7641,11 +7665,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7663,11 +7687,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7685,11 +7709,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7707,11 +7731,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -7729,11 +7753,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -7751,11 +7775,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -7773,11 +7797,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -7795,11 +7819,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -7817,11 +7841,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -7839,11 +7863,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -7861,11 +7885,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -7883,11 +7907,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -7905,11 +7929,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -7927,11 +7951,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -7949,11 +7973,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -7971,11 +7995,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -7993,11 +8017,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8015,11 +8039,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8037,11 +8061,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8059,11 +8083,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8081,11 +8105,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8103,11 +8127,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8125,11 +8149,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8147,11 +8171,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8169,11 +8193,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8191,11 +8215,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8213,11 +8237,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8235,11 +8259,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8257,11 +8281,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8279,11 +8303,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8301,11 +8325,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8323,11 +8347,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8345,11 +8369,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8367,11 +8391,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8389,11 +8413,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8411,11 +8435,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="24">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="26">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="25">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="27">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8433,11 +8457,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8455,11 +8479,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8477,11 +8501,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8499,11 +8523,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8521,11 +8545,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8543,11 +8567,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8565,11 +8589,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8587,11 +8611,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8609,11 +8633,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8631,11 +8655,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8653,11 +8677,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8675,11 +8699,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8697,11 +8721,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8719,11 +8743,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -8741,11 +8765,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -8763,11 +8787,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -8785,11 +8809,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -8807,11 +8831,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -8829,11 +8853,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -8851,11 +8875,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -8873,11 +8897,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -8895,11 +8919,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -8917,11 +8941,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -8939,11 +8963,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -8961,11 +8985,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -8983,11 +9007,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9005,11 +9029,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9027,11 +9051,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9049,11 +9073,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9071,11 +9095,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9093,11 +9117,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9115,11 +9139,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9137,11 +9161,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9159,11 +9183,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9181,11 +9205,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9203,11 +9227,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9225,11 +9249,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9247,11 +9271,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9269,11 +9293,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9291,11 +9315,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9313,11 +9337,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9335,11 +9359,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9357,11 +9381,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9379,11 +9403,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9401,11 +9425,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9423,11 +9447,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9445,11 +9469,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9467,11 +9491,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9489,11 +9513,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9511,11 +9535,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9533,11 +9557,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9555,11 +9579,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9577,11 +9601,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9599,11 +9623,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9621,11 +9645,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9643,11 +9667,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9665,11 +9689,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9687,11 +9711,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -9709,11 +9733,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -9731,11 +9755,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -9753,11 +9777,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -9775,11 +9799,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -9797,11 +9821,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -9819,11 +9843,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="26">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="28">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="27">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="29">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -9841,11 +9865,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -9863,11 +9887,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -9885,11 +9909,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -9907,11 +9931,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -9929,11 +9953,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -9951,11 +9975,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -9973,11 +9997,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -9995,11 +10019,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10017,11 +10041,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10039,11 +10063,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10061,11 +10085,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF6DD86-2D9C-4EF6-AC72-BC5F80DA99B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3B6C35-8A59-4348-982F-154F548B15DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1686,27 +1686,27 @@
         <v>30</v>
       </c>
       <c r="F20" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
         <v>60</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" ref="I20" si="16">IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
-        <v>1030</v>
+        <v>980</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" ref="J20" si="17">IF(I20="","",1440-I20)</f>
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M20" s="16" t="s">
         <v>58</v>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3B6C35-8A59-4348-982F-154F548B15DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3464A127-134F-4317-8C34-C458D6D72B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>Today, I worked on DSA, SQL Queries and College Subjects.</t>
+  </si>
+  <si>
+    <t>Today, I worked on DSA and Python College Subjects.</t>
   </si>
 </sst>
 </file>
@@ -1715,27 +1718,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="12"/>
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B21" s="14">
+        <v>450</v>
+      </c>
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>60</v>
+      </c>
+      <c r="E21" s="14">
+        <v>120</v>
+      </c>
+      <c r="F21" s="14">
+        <v>300</v>
+      </c>
+      <c r="G21" s="14">
+        <v>6</v>
+      </c>
+      <c r="H21" s="14">
+        <v>60</v>
+      </c>
+      <c r="I21" s="15">
+        <f t="shared" ref="I21" si="18">IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
+        <v>990</v>
+      </c>
+      <c r="J21" s="15">
+        <f t="shared" ref="J21" si="19">IF(I21="","",1440-I21)</f>
+        <v>450</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
@@ -2803,11 +2830,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="18">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="20">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="19">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="21">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -2825,11 +2852,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -2847,11 +2874,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -2869,11 +2896,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -2891,11 +2918,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -2913,11 +2940,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -2935,11 +2962,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -2957,11 +2984,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -2979,11 +3006,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3001,11 +3028,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3023,11 +3050,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3045,11 +3072,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3067,11 +3094,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3089,11 +3116,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3111,11 +3138,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3133,11 +3160,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3155,11 +3182,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3177,11 +3204,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3199,11 +3226,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3221,11 +3248,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3243,11 +3270,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3265,11 +3292,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3287,11 +3314,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3309,11 +3336,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3331,11 +3358,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3353,11 +3380,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3375,11 +3402,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3397,11 +3424,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3419,11 +3446,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3441,11 +3468,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3463,11 +3490,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3485,11 +3512,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3507,11 +3534,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3529,11 +3556,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3551,11 +3578,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3573,11 +3600,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3595,11 +3622,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3617,11 +3644,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3639,11 +3666,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3661,11 +3688,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3683,11 +3710,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3705,11 +3732,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3727,11 +3754,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3749,11 +3776,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3771,11 +3798,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3793,11 +3820,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3815,11 +3842,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -3837,11 +3864,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -3859,11 +3886,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -3881,11 +3908,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -3903,11 +3930,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -3925,11 +3952,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -3947,11 +3974,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -3969,11 +3996,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -3991,11 +4018,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4013,11 +4040,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4035,11 +4062,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4057,11 +4084,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4079,11 +4106,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4101,11 +4128,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4123,11 +4150,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4145,11 +4172,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4167,11 +4194,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4189,11 +4216,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4211,11 +4238,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="20">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="22">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="21">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="23">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4233,11 +4260,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4255,11 +4282,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4277,11 +4304,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4299,11 +4326,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4321,11 +4348,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4343,11 +4370,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4365,11 +4392,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4387,11 +4414,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4409,11 +4436,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4431,11 +4458,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4453,11 +4480,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4475,11 +4502,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4497,11 +4524,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4519,11 +4546,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4541,11 +4568,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4563,11 +4590,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4585,11 +4612,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4607,11 +4634,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4629,11 +4656,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4651,11 +4678,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4673,11 +4700,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4695,11 +4722,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4717,11 +4744,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4739,11 +4766,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -4761,11 +4788,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -4783,11 +4810,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -4805,11 +4832,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -4827,11 +4854,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -4849,11 +4876,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -4871,11 +4898,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -4893,11 +4920,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -4915,11 +4942,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -4937,11 +4964,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -4959,11 +4986,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -4981,11 +5008,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5003,11 +5030,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5025,11 +5052,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5047,11 +5074,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5069,11 +5096,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5091,11 +5118,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5113,11 +5140,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5135,11 +5162,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5157,11 +5184,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5179,11 +5206,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5201,11 +5228,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5223,11 +5250,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5245,11 +5272,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5267,11 +5294,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5289,11 +5316,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5311,11 +5338,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5333,11 +5360,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5355,11 +5382,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5377,11 +5404,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5399,11 +5426,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5421,11 +5448,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5443,11 +5470,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5465,11 +5492,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5487,11 +5514,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5509,11 +5536,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5531,11 +5558,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5553,11 +5580,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5575,11 +5602,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5597,11 +5624,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5619,11 +5646,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="22">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="24">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="23">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="25">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5641,11 +5668,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5663,11 +5690,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5685,11 +5712,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5707,11 +5734,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5729,11 +5756,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -5751,11 +5778,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -5773,11 +5800,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -5795,11 +5822,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -5817,11 +5844,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -5839,11 +5866,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -5861,11 +5888,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -5883,11 +5910,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -5905,11 +5932,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -5927,11 +5954,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -5949,11 +5976,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -5971,11 +5998,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -5993,11 +6020,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6015,11 +6042,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6037,11 +6064,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6059,11 +6086,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6081,11 +6108,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6103,11 +6130,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6125,11 +6152,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6147,11 +6174,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6169,11 +6196,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6191,11 +6218,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6213,11 +6240,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6235,11 +6262,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6257,11 +6284,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6279,11 +6306,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6301,11 +6328,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6323,11 +6350,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6345,11 +6372,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6367,11 +6394,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6389,11 +6416,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6411,11 +6438,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6433,11 +6460,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6455,11 +6482,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6477,11 +6504,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6499,11 +6526,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6521,11 +6548,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6543,11 +6570,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6565,11 +6592,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6587,11 +6614,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6609,11 +6636,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6631,11 +6658,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6653,11 +6680,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6675,11 +6702,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6697,11 +6724,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6719,11 +6746,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6741,11 +6768,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -6763,11 +6790,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -6785,11 +6812,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -6807,11 +6834,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -6829,11 +6856,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -6851,11 +6878,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -6873,11 +6900,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -6895,11 +6922,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -6917,11 +6944,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -6939,11 +6966,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -6961,11 +6988,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -6983,11 +7010,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7005,11 +7032,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7027,11 +7054,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="24">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="26">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="25">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="27">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7049,11 +7076,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7071,11 +7098,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7093,11 +7120,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7115,11 +7142,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7137,11 +7164,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7159,11 +7186,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7181,11 +7208,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7203,11 +7230,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7225,11 +7252,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7247,11 +7274,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7269,11 +7296,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7291,11 +7318,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7313,11 +7340,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7335,11 +7362,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7357,11 +7384,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7379,11 +7406,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7401,11 +7428,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7423,11 +7450,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7445,11 +7472,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7467,11 +7494,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7489,11 +7516,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7511,11 +7538,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7533,11 +7560,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7555,11 +7582,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7577,11 +7604,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7599,11 +7626,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7621,11 +7648,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7643,11 +7670,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7665,11 +7692,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7687,11 +7714,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7709,11 +7736,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7731,11 +7758,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -7753,11 +7780,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -7775,11 +7802,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -7797,11 +7824,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -7819,11 +7846,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -7841,11 +7868,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -7863,11 +7890,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -7885,11 +7912,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -7907,11 +7934,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -7929,11 +7956,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -7951,11 +7978,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -7973,11 +8000,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -7995,11 +8022,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8017,11 +8044,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8039,11 +8066,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8061,11 +8088,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8083,11 +8110,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8105,11 +8132,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8127,11 +8154,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8149,11 +8176,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8171,11 +8198,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8193,11 +8220,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8215,11 +8242,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8237,11 +8264,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8259,11 +8286,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8281,11 +8308,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8303,11 +8330,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8325,11 +8352,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8347,11 +8374,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8369,11 +8396,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8391,11 +8418,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8413,11 +8440,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8435,11 +8462,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="26">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="28">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="27">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="29">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8457,11 +8484,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8479,11 +8506,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8501,11 +8528,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8523,11 +8550,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8545,11 +8572,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8567,11 +8594,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8589,11 +8616,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8611,11 +8638,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8633,11 +8660,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8655,11 +8682,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8677,11 +8704,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8699,11 +8726,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8721,11 +8748,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8743,11 +8770,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -8765,11 +8792,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -8787,11 +8814,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -8809,11 +8836,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -8831,11 +8858,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -8853,11 +8880,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -8875,11 +8902,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -8897,11 +8924,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -8919,11 +8946,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -8941,11 +8968,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -8963,11 +8990,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -8985,11 +9012,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9007,11 +9034,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9029,11 +9056,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9051,11 +9078,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9073,11 +9100,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9095,11 +9122,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9117,11 +9144,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9139,11 +9166,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9161,11 +9188,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9183,11 +9210,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9205,11 +9232,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9227,11 +9254,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9249,11 +9276,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9271,11 +9298,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9293,11 +9320,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9315,11 +9342,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9337,11 +9364,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9359,11 +9386,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9381,11 +9408,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9403,11 +9430,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9425,11 +9452,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9447,11 +9474,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9469,11 +9496,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9491,11 +9518,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9513,11 +9540,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9535,11 +9562,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9557,11 +9584,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9579,11 +9606,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9601,11 +9628,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9623,11 +9650,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9645,11 +9672,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9667,11 +9694,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9689,11 +9716,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9711,11 +9738,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -9733,11 +9760,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -9755,11 +9782,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -9777,11 +9804,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -9799,11 +9826,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -9821,11 +9848,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -9843,11 +9870,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="28">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="30">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="29">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="31">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -9865,11 +9892,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -9887,11 +9914,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -9909,11 +9936,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -9931,11 +9958,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -9953,11 +9980,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -9975,11 +10002,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -9997,11 +10024,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10019,11 +10046,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10041,11 +10068,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10063,11 +10090,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10085,11 +10112,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3464A127-134F-4317-8C34-C458D6D72B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDE3537-4B3A-4AC2-A460-501F0D4F63C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1735,21 +1735,21 @@
         <v>120</v>
       </c>
       <c r="F21" s="14">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G21" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H21" s="14">
         <v>60</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" ref="I21" si="18">IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
-        <v>990</v>
+        <v>1040</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" ref="J21" si="19">IF(I21="","",1440-I21)</f>
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>49</v>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDE3537-4B3A-4AC2-A460-501F0D4F63C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF85159-7627-425A-836E-A52499B5E712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -945,7 +945,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="20">
-        <v>12625731</v>
+        <v>12626731</v>
       </c>
       <c r="G2" s="20"/>
     </row>
@@ -1764,27 +1764,51 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="12"/>
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B22" s="14">
+        <v>450</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>210</v>
+      </c>
+      <c r="E22" s="14">
+        <v>60</v>
+      </c>
+      <c r="F22" s="14">
+        <v>200</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>60</v>
+      </c>
+      <c r="I22" s="15">
+        <f t="shared" ref="I22" si="20">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
+        <v>980</v>
+      </c>
+      <c r="J22" s="15">
+        <f t="shared" ref="J22" si="21">IF(I22="","",1440-I22)</f>
+        <v>460</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
@@ -2830,11 +2854,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="20">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="22">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="21">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="23">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -2852,11 +2876,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -2874,11 +2898,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -2896,11 +2920,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -2918,11 +2942,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -2940,11 +2964,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -2962,11 +2986,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -2984,11 +3008,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3006,11 +3030,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3028,11 +3052,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3050,11 +3074,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3072,11 +3096,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3094,11 +3118,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3116,11 +3140,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3138,11 +3162,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3160,11 +3184,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3182,11 +3206,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3204,11 +3228,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3226,11 +3250,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3248,11 +3272,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3270,11 +3294,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3292,11 +3316,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3314,11 +3338,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3336,11 +3360,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3358,11 +3382,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3380,11 +3404,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3402,11 +3426,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3424,11 +3448,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3446,11 +3470,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3468,11 +3492,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3490,11 +3514,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3512,11 +3536,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3534,11 +3558,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3556,11 +3580,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3578,11 +3602,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3600,11 +3624,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3622,11 +3646,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3644,11 +3668,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3666,11 +3690,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3688,11 +3712,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3710,11 +3734,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3732,11 +3756,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3754,11 +3778,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3776,11 +3800,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3798,11 +3822,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3820,11 +3844,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3842,11 +3866,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -3864,11 +3888,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -3886,11 +3910,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -3908,11 +3932,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -3930,11 +3954,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -3952,11 +3976,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -3974,11 +3998,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -3996,11 +4020,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4018,11 +4042,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4040,11 +4064,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4062,11 +4086,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4084,11 +4108,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4106,11 +4130,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4128,11 +4152,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4150,11 +4174,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4172,11 +4196,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4194,11 +4218,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4216,11 +4240,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4238,11 +4262,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="22">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="24">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="23">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="25">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4260,11 +4284,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4282,11 +4306,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4304,11 +4328,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4326,11 +4350,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4348,11 +4372,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4370,11 +4394,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4392,11 +4416,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4414,11 +4438,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4436,11 +4460,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4458,11 +4482,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4480,11 +4504,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4502,11 +4526,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4524,11 +4548,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4546,11 +4570,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4568,11 +4592,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4590,11 +4614,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4612,11 +4636,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4634,11 +4658,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4656,11 +4680,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4678,11 +4702,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4700,11 +4724,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4722,11 +4746,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4744,11 +4768,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4766,11 +4790,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -4788,11 +4812,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -4810,11 +4834,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -4832,11 +4856,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -4854,11 +4878,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -4876,11 +4900,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -4898,11 +4922,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -4920,11 +4944,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -4942,11 +4966,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -4964,11 +4988,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -4986,11 +5010,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5008,11 +5032,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5030,11 +5054,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5052,11 +5076,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5074,11 +5098,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5096,11 +5120,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5118,11 +5142,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5140,11 +5164,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5162,11 +5186,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5184,11 +5208,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5206,11 +5230,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5228,11 +5252,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5250,11 +5274,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5272,11 +5296,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5294,11 +5318,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5316,11 +5340,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5338,11 +5362,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5360,11 +5384,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5382,11 +5406,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5404,11 +5428,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5426,11 +5450,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5448,11 +5472,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5470,11 +5494,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5492,11 +5516,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5514,11 +5538,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5536,11 +5560,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5558,11 +5582,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5580,11 +5604,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5602,11 +5626,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5624,11 +5648,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5646,11 +5670,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="24">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="26">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="25">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="27">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5668,11 +5692,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5690,11 +5714,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5712,11 +5736,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5734,11 +5758,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5756,11 +5780,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -5778,11 +5802,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -5800,11 +5824,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -5822,11 +5846,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -5844,11 +5868,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -5866,11 +5890,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -5888,11 +5912,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -5910,11 +5934,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -5932,11 +5956,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -5954,11 +5978,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -5976,11 +6000,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -5998,11 +6022,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6020,11 +6044,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6042,11 +6066,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6064,11 +6088,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6086,11 +6110,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6108,11 +6132,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6130,11 +6154,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6152,11 +6176,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6174,11 +6198,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6196,11 +6220,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6218,11 +6242,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6240,11 +6264,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6262,11 +6286,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6284,11 +6308,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6306,11 +6330,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6328,11 +6352,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6350,11 +6374,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6372,11 +6396,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6394,11 +6418,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6416,11 +6440,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6438,11 +6462,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6460,11 +6484,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6482,11 +6506,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6504,11 +6528,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6526,11 +6550,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6548,11 +6572,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6570,11 +6594,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6592,11 +6616,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6614,11 +6638,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6636,11 +6660,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6658,11 +6682,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6680,11 +6704,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6702,11 +6726,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6724,11 +6748,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6746,11 +6770,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6768,11 +6792,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -6790,11 +6814,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -6812,11 +6836,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -6834,11 +6858,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -6856,11 +6880,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -6878,11 +6902,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -6900,11 +6924,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -6922,11 +6946,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -6944,11 +6968,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -6966,11 +6990,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -6988,11 +7012,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7010,11 +7034,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7032,11 +7056,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7054,11 +7078,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="26">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="28">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="27">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="29">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7076,11 +7100,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7098,11 +7122,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7120,11 +7144,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7142,11 +7166,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7164,11 +7188,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7186,11 +7210,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7208,11 +7232,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7230,11 +7254,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7252,11 +7276,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7274,11 +7298,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7296,11 +7320,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7318,11 +7342,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7340,11 +7364,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7362,11 +7386,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7384,11 +7408,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7406,11 +7430,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7428,11 +7452,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7450,11 +7474,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7472,11 +7496,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7494,11 +7518,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7516,11 +7540,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7538,11 +7562,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7560,11 +7584,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7582,11 +7606,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7604,11 +7628,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7626,11 +7650,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7648,11 +7672,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7670,11 +7694,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7692,11 +7716,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7714,11 +7738,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7736,11 +7760,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7758,11 +7782,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -7780,11 +7804,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -7802,11 +7826,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -7824,11 +7848,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -7846,11 +7870,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -7868,11 +7892,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -7890,11 +7914,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -7912,11 +7936,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -7934,11 +7958,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -7956,11 +7980,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -7978,11 +8002,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8000,11 +8024,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8022,11 +8046,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8044,11 +8068,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8066,11 +8090,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8088,11 +8112,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8110,11 +8134,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8132,11 +8156,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8154,11 +8178,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8176,11 +8200,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8198,11 +8222,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8220,11 +8244,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8242,11 +8266,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8264,11 +8288,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8286,11 +8310,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8308,11 +8332,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8330,11 +8354,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8352,11 +8376,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8374,11 +8398,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8396,11 +8420,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8418,11 +8442,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8440,11 +8464,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8462,11 +8486,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="28">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="30">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="29">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="31">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8484,11 +8508,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8506,11 +8530,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8528,11 +8552,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8550,11 +8574,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8572,11 +8596,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8594,11 +8618,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8616,11 +8640,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8638,11 +8662,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8660,11 +8684,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8682,11 +8706,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8704,11 +8728,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8726,11 +8750,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8748,11 +8772,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8770,11 +8794,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -8792,11 +8816,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -8814,11 +8838,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -8836,11 +8860,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -8858,11 +8882,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -8880,11 +8904,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -8902,11 +8926,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -8924,11 +8948,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -8946,11 +8970,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -8968,11 +8992,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -8990,11 +9014,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9012,11 +9036,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9034,11 +9058,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9056,11 +9080,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9078,11 +9102,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9100,11 +9124,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9122,11 +9146,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9144,11 +9168,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9166,11 +9190,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9188,11 +9212,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9210,11 +9234,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9232,11 +9256,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9254,11 +9278,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9276,11 +9300,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9298,11 +9322,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9320,11 +9344,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9342,11 +9366,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9364,11 +9388,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9386,11 +9410,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9408,11 +9432,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9430,11 +9454,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9452,11 +9476,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9474,11 +9498,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9496,11 +9520,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9518,11 +9542,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9540,11 +9564,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9562,11 +9586,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9584,11 +9608,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9606,11 +9630,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9628,11 +9652,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9650,11 +9674,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9672,11 +9696,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9694,11 +9718,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9716,11 +9740,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9738,11 +9762,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -9760,11 +9784,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -9782,11 +9806,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -9804,11 +9828,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -9826,11 +9850,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -9848,11 +9872,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -9870,11 +9894,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="30">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="32">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="31">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="33">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -9892,11 +9916,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -9914,11 +9938,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -9936,11 +9960,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -9958,11 +9982,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -9980,11 +10004,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10002,11 +10026,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10024,11 +10048,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10046,11 +10070,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10068,11 +10092,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10090,11 +10114,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10112,11 +10136,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF85159-7627-425A-836E-A52499B5E712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A02030-579A-41B7-A144-BF6C97BD9D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1810,27 +1810,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="12"/>
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B23" s="14">
+        <v>450</v>
+      </c>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
+        <v>60</v>
+      </c>
+      <c r="E23" s="14">
+        <v>20</v>
+      </c>
+      <c r="F23" s="14">
+        <v>150</v>
+      </c>
+      <c r="G23" s="14">
+        <v>3</v>
+      </c>
+      <c r="H23" s="14">
+        <v>60</v>
+      </c>
+      <c r="I23" s="15">
+        <f t="shared" ref="I23" si="22">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
+        <v>740</v>
+      </c>
+      <c r="J23" s="15">
+        <f t="shared" ref="J23" si="23">IF(I23="","",1440-I23)</f>
+        <v>700</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
@@ -2854,11 +2878,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="22">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="24">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="23">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="25">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -2876,11 +2900,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -2898,11 +2922,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -2920,11 +2944,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -2942,11 +2966,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -2964,11 +2988,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -2986,11 +3010,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3008,11 +3032,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3030,11 +3054,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3052,11 +3076,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3074,11 +3098,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3096,11 +3120,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3118,11 +3142,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3140,11 +3164,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3162,11 +3186,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3184,11 +3208,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3206,11 +3230,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3228,11 +3252,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3250,11 +3274,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3272,11 +3296,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3294,11 +3318,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3316,11 +3340,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3338,11 +3362,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3360,11 +3384,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3382,11 +3406,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3404,11 +3428,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3426,11 +3450,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3448,11 +3472,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3470,11 +3494,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3492,11 +3516,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3514,11 +3538,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3536,11 +3560,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3558,11 +3582,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3580,11 +3604,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3602,11 +3626,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3624,11 +3648,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3646,11 +3670,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3668,11 +3692,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3690,11 +3714,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3712,11 +3736,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3734,11 +3758,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3756,11 +3780,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3778,11 +3802,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3800,11 +3824,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3822,11 +3846,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3844,11 +3868,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3866,11 +3890,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -3888,11 +3912,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -3910,11 +3934,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -3932,11 +3956,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -3954,11 +3978,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -3976,11 +4000,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -3998,11 +4022,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4020,11 +4044,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4042,11 +4066,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4064,11 +4088,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4086,11 +4110,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4108,11 +4132,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4130,11 +4154,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4152,11 +4176,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4174,11 +4198,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4196,11 +4220,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4218,11 +4242,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4240,11 +4264,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4262,11 +4286,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="24">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="26">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="25">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="27">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4284,11 +4308,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4306,11 +4330,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4328,11 +4352,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4350,11 +4374,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4372,11 +4396,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4394,11 +4418,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4416,11 +4440,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4438,11 +4462,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4460,11 +4484,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4482,11 +4506,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4504,11 +4528,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4526,11 +4550,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4548,11 +4572,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4570,11 +4594,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4592,11 +4616,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4614,11 +4638,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4636,11 +4660,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4658,11 +4682,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4680,11 +4704,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4702,11 +4726,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4724,11 +4748,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4746,11 +4770,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4768,11 +4792,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4790,11 +4814,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -4812,11 +4836,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -4834,11 +4858,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -4856,11 +4880,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -4878,11 +4902,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -4900,11 +4924,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -4922,11 +4946,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -4944,11 +4968,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -4966,11 +4990,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -4988,11 +5012,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5010,11 +5034,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5032,11 +5056,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5054,11 +5078,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5076,11 +5100,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5098,11 +5122,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5120,11 +5144,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5142,11 +5166,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5164,11 +5188,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5186,11 +5210,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5208,11 +5232,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5230,11 +5254,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5252,11 +5276,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5274,11 +5298,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5296,11 +5320,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5318,11 +5342,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5340,11 +5364,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5362,11 +5386,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5384,11 +5408,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5406,11 +5430,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5428,11 +5452,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5450,11 +5474,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5472,11 +5496,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5494,11 +5518,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5516,11 +5540,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5538,11 +5562,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5560,11 +5584,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5582,11 +5606,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5604,11 +5628,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5626,11 +5650,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5648,11 +5672,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5670,11 +5694,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="26">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="28">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="27">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="29">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5692,11 +5716,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5714,11 +5738,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5736,11 +5760,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5758,11 +5782,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5780,11 +5804,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -5802,11 +5826,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -5824,11 +5848,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -5846,11 +5870,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -5868,11 +5892,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -5890,11 +5914,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -5912,11 +5936,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -5934,11 +5958,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -5956,11 +5980,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -5978,11 +6002,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6000,11 +6024,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6022,11 +6046,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6044,11 +6068,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6066,11 +6090,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6088,11 +6112,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6110,11 +6134,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6132,11 +6156,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6154,11 +6178,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6176,11 +6200,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6198,11 +6222,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6220,11 +6244,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6242,11 +6266,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6264,11 +6288,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6286,11 +6310,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6308,11 +6332,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6330,11 +6354,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6352,11 +6376,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6374,11 +6398,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6396,11 +6420,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6418,11 +6442,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6440,11 +6464,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6462,11 +6486,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6484,11 +6508,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6506,11 +6530,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6528,11 +6552,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6550,11 +6574,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6572,11 +6596,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6594,11 +6618,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6616,11 +6640,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6638,11 +6662,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6660,11 +6684,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6682,11 +6706,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6704,11 +6728,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6726,11 +6750,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6748,11 +6772,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6770,11 +6794,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6792,11 +6816,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -6814,11 +6838,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -6836,11 +6860,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -6858,11 +6882,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -6880,11 +6904,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -6902,11 +6926,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -6924,11 +6948,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -6946,11 +6970,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -6968,11 +6992,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -6990,11 +7014,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7012,11 +7036,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7034,11 +7058,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7056,11 +7080,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7078,11 +7102,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="28">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="30">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="29">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="31">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7100,11 +7124,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7122,11 +7146,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7144,11 +7168,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7166,11 +7190,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7188,11 +7212,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7210,11 +7234,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7232,11 +7256,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7254,11 +7278,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7276,11 +7300,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7298,11 +7322,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7320,11 +7344,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7342,11 +7366,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7364,11 +7388,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7386,11 +7410,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7408,11 +7432,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7430,11 +7454,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7452,11 +7476,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7474,11 +7498,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7496,11 +7520,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7518,11 +7542,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7540,11 +7564,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7562,11 +7586,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7584,11 +7608,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7606,11 +7630,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7628,11 +7652,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7650,11 +7674,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7672,11 +7696,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7694,11 +7718,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7716,11 +7740,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7738,11 +7762,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7760,11 +7784,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7782,11 +7806,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -7804,11 +7828,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -7826,11 +7850,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -7848,11 +7872,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -7870,11 +7894,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -7892,11 +7916,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -7914,11 +7938,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -7936,11 +7960,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -7958,11 +7982,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -7980,11 +8004,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8002,11 +8026,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8024,11 +8048,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8046,11 +8070,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8068,11 +8092,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8090,11 +8114,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8112,11 +8136,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8134,11 +8158,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8156,11 +8180,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8178,11 +8202,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8200,11 +8224,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8222,11 +8246,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8244,11 +8268,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8266,11 +8290,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8288,11 +8312,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8310,11 +8334,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8332,11 +8356,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8354,11 +8378,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8376,11 +8400,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8398,11 +8422,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8420,11 +8444,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8442,11 +8466,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8464,11 +8488,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8486,11 +8510,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="30">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="32">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="31">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="33">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8508,11 +8532,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8530,11 +8554,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8552,11 +8576,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8574,11 +8598,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8596,11 +8620,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8618,11 +8642,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8640,11 +8664,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8662,11 +8686,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8684,11 +8708,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8706,11 +8730,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8728,11 +8752,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8750,11 +8774,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8772,11 +8796,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8794,11 +8818,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -8816,11 +8840,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -8838,11 +8862,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -8860,11 +8884,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -8882,11 +8906,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -8904,11 +8928,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -8926,11 +8950,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -8948,11 +8972,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -8970,11 +8994,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -8992,11 +9016,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9014,11 +9038,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9036,11 +9060,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9058,11 +9082,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9080,11 +9104,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9102,11 +9126,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9124,11 +9148,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9146,11 +9170,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9168,11 +9192,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9190,11 +9214,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9212,11 +9236,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9234,11 +9258,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9256,11 +9280,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9278,11 +9302,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9300,11 +9324,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9322,11 +9346,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9344,11 +9368,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9366,11 +9390,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9388,11 +9412,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9410,11 +9434,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9432,11 +9456,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9454,11 +9478,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9476,11 +9500,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9498,11 +9522,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9520,11 +9544,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9542,11 +9566,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9564,11 +9588,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9586,11 +9610,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9608,11 +9632,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9630,11 +9654,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9652,11 +9676,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9674,11 +9698,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9696,11 +9720,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9718,11 +9742,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9740,11 +9764,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9762,11 +9786,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -9784,11 +9808,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -9806,11 +9830,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -9828,11 +9852,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -9850,11 +9874,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -9872,11 +9896,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -9894,11 +9918,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="32">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="34">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="33">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="35">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -9916,11 +9940,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -9938,11 +9962,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -9960,11 +9984,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -9982,11 +10006,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10004,11 +10028,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10026,11 +10050,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10048,11 +10072,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10070,11 +10094,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10092,11 +10116,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10114,11 +10138,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10136,11 +10160,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A02030-579A-41B7-A144-BF6C97BD9D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D6E675-ED50-4CF6-B830-F66C7F56509C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1856,27 +1856,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="12"/>
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B24" s="14">
+        <v>450</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>20</v>
+      </c>
+      <c r="F24" s="14">
+        <v>50</v>
+      </c>
+      <c r="G24" s="14">
+        <v>1</v>
+      </c>
+      <c r="H24" s="14">
+        <v>60</v>
+      </c>
+      <c r="I24" s="15">
+        <f t="shared" ref="I24" si="24">IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
+        <v>700</v>
+      </c>
+      <c r="J24" s="15">
+        <f t="shared" ref="J24" si="25">IF(I24="","",1440-I24)</f>
+        <v>740</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
@@ -2878,11 +2902,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="24">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="26">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="25">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="27">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -2900,11 +2924,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -2922,11 +2946,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -2944,11 +2968,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -2966,11 +2990,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -2988,11 +3012,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3010,11 +3034,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3032,11 +3056,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3054,11 +3078,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3076,11 +3100,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3098,11 +3122,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3120,11 +3144,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3142,11 +3166,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3164,11 +3188,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3186,11 +3210,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3208,11 +3232,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3230,11 +3254,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3252,11 +3276,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3274,11 +3298,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3296,11 +3320,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3318,11 +3342,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3340,11 +3364,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3362,11 +3386,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3384,11 +3408,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3406,11 +3430,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3428,11 +3452,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3450,11 +3474,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3472,11 +3496,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3494,11 +3518,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3516,11 +3540,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3538,11 +3562,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3560,11 +3584,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3582,11 +3606,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3604,11 +3628,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3626,11 +3650,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3648,11 +3672,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3670,11 +3694,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3692,11 +3716,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3714,11 +3738,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3736,11 +3760,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3758,11 +3782,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3780,11 +3804,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3802,11 +3826,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3824,11 +3848,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3846,11 +3870,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3868,11 +3892,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3890,11 +3914,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -3912,11 +3936,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -3934,11 +3958,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -3956,11 +3980,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -3978,11 +4002,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4000,11 +4024,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4022,11 +4046,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4044,11 +4068,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4066,11 +4090,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4088,11 +4112,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4110,11 +4134,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4132,11 +4156,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4154,11 +4178,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4176,11 +4200,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4198,11 +4222,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4220,11 +4244,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4242,11 +4266,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4264,11 +4288,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4286,11 +4310,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="26">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="28">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="27">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="29">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4308,11 +4332,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4330,11 +4354,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4352,11 +4376,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4374,11 +4398,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4396,11 +4420,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4418,11 +4442,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4440,11 +4464,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4462,11 +4486,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4484,11 +4508,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4506,11 +4530,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4528,11 +4552,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4550,11 +4574,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4572,11 +4596,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4594,11 +4618,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4616,11 +4640,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4638,11 +4662,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4660,11 +4684,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4682,11 +4706,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4704,11 +4728,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4726,11 +4750,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4748,11 +4772,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4770,11 +4794,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4792,11 +4816,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4814,11 +4838,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -4836,11 +4860,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -4858,11 +4882,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -4880,11 +4904,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -4902,11 +4926,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -4924,11 +4948,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -4946,11 +4970,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -4968,11 +4992,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -4990,11 +5014,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5012,11 +5036,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5034,11 +5058,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5056,11 +5080,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5078,11 +5102,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5100,11 +5124,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5122,11 +5146,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5144,11 +5168,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5166,11 +5190,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5188,11 +5212,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5210,11 +5234,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5232,11 +5256,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5254,11 +5278,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5276,11 +5300,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5298,11 +5322,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5320,11 +5344,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5342,11 +5366,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5364,11 +5388,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5386,11 +5410,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5408,11 +5432,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5430,11 +5454,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5452,11 +5476,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5474,11 +5498,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5496,11 +5520,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5518,11 +5542,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5540,11 +5564,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5562,11 +5586,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5584,11 +5608,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5606,11 +5630,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5628,11 +5652,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5650,11 +5674,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5672,11 +5696,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5694,11 +5718,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="28">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="30">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="29">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="31">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5716,11 +5740,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5738,11 +5762,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5760,11 +5784,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5782,11 +5806,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5804,11 +5828,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -5826,11 +5850,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -5848,11 +5872,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -5870,11 +5894,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -5892,11 +5916,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -5914,11 +5938,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -5936,11 +5960,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -5958,11 +5982,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -5980,11 +6004,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6002,11 +6026,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6024,11 +6048,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6046,11 +6070,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6068,11 +6092,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6090,11 +6114,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6112,11 +6136,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6134,11 +6158,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6156,11 +6180,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6178,11 +6202,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6200,11 +6224,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6222,11 +6246,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6244,11 +6268,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6266,11 +6290,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6288,11 +6312,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6310,11 +6334,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6332,11 +6356,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6354,11 +6378,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6376,11 +6400,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6398,11 +6422,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6420,11 +6444,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6442,11 +6466,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6464,11 +6488,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6486,11 +6510,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6508,11 +6532,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6530,11 +6554,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6552,11 +6576,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6574,11 +6598,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6596,11 +6620,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6618,11 +6642,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6640,11 +6664,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6662,11 +6686,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6684,11 +6708,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6706,11 +6730,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6728,11 +6752,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6750,11 +6774,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6772,11 +6796,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6794,11 +6818,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6816,11 +6840,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -6838,11 +6862,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -6860,11 +6884,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -6882,11 +6906,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -6904,11 +6928,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -6926,11 +6950,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -6948,11 +6972,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -6970,11 +6994,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -6992,11 +7016,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7014,11 +7038,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7036,11 +7060,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7058,11 +7082,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7080,11 +7104,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7102,11 +7126,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="30">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="32">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="31">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="33">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7124,11 +7148,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7146,11 +7170,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7168,11 +7192,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7190,11 +7214,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7212,11 +7236,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7234,11 +7258,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7256,11 +7280,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7278,11 +7302,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7300,11 +7324,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7322,11 +7346,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7344,11 +7368,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7366,11 +7390,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7388,11 +7412,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7410,11 +7434,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7432,11 +7456,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7454,11 +7478,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7476,11 +7500,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7498,11 +7522,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7520,11 +7544,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7542,11 +7566,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7564,11 +7588,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7586,11 +7610,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7608,11 +7632,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7630,11 +7654,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7652,11 +7676,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7674,11 +7698,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7696,11 +7720,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7718,11 +7742,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7740,11 +7764,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7762,11 +7786,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7784,11 +7808,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7806,11 +7830,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -7828,11 +7852,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -7850,11 +7874,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -7872,11 +7896,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -7894,11 +7918,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -7916,11 +7940,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -7938,11 +7962,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -7960,11 +7984,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -7982,11 +8006,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8004,11 +8028,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8026,11 +8050,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8048,11 +8072,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8070,11 +8094,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8092,11 +8116,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8114,11 +8138,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8136,11 +8160,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8158,11 +8182,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8180,11 +8204,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8202,11 +8226,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8224,11 +8248,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8246,11 +8270,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8268,11 +8292,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8290,11 +8314,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8312,11 +8336,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8334,11 +8358,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8356,11 +8380,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8378,11 +8402,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8400,11 +8424,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8422,11 +8446,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8444,11 +8468,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8466,11 +8490,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8488,11 +8512,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8510,11 +8534,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="32">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="34">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="33">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="35">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8532,11 +8556,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8554,11 +8578,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8576,11 +8600,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8598,11 +8622,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8620,11 +8644,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8642,11 +8666,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8664,11 +8688,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8686,11 +8710,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8708,11 +8732,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8730,11 +8754,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8752,11 +8776,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8774,11 +8798,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8796,11 +8820,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8818,11 +8842,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -8840,11 +8864,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -8862,11 +8886,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -8884,11 +8908,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -8906,11 +8930,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -8928,11 +8952,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -8950,11 +8974,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -8972,11 +8996,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -8994,11 +9018,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9016,11 +9040,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9038,11 +9062,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9060,11 +9084,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9082,11 +9106,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9104,11 +9128,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9126,11 +9150,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9148,11 +9172,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9170,11 +9194,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9192,11 +9216,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9214,11 +9238,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9236,11 +9260,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9258,11 +9282,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9280,11 +9304,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9302,11 +9326,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9324,11 +9348,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9346,11 +9370,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9368,11 +9392,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9390,11 +9414,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9412,11 +9436,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9434,11 +9458,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9456,11 +9480,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9478,11 +9502,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9500,11 +9524,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9522,11 +9546,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9544,11 +9568,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9566,11 +9590,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9588,11 +9612,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9610,11 +9634,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9632,11 +9656,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9654,11 +9678,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9676,11 +9700,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9698,11 +9722,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9720,11 +9744,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9742,11 +9766,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9764,11 +9788,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9786,11 +9810,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -9808,11 +9832,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -9830,11 +9854,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -9852,11 +9876,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -9874,11 +9898,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -9896,11 +9920,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -9918,11 +9942,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="34">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="36">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="35">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="37">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -9940,11 +9964,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -9962,11 +9986,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -9984,11 +10008,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10006,11 +10030,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10028,11 +10052,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10050,11 +10074,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10072,11 +10096,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10094,11 +10118,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10116,11 +10140,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10138,11 +10162,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10160,11 +10184,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D6E675-ED50-4CF6-B830-F66C7F56509C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE798647-8EB0-4BD8-90EE-C53601B2EF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>Today, I worked on DSA and Python College Subjects.</t>
+  </si>
+  <si>
+    <t>Today, I worked on CA Practice and College Subjects.</t>
   </si>
 </sst>
 </file>
@@ -1902,27 +1905,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="12"/>
+    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B25" s="14">
+        <v>450</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>60</v>
+      </c>
+      <c r="E25" s="14">
+        <v>30</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>60</v>
+      </c>
+      <c r="I25" s="15">
+        <f t="shared" ref="I25" si="26">IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
+        <v>600</v>
+      </c>
+      <c r="J25" s="15">
+        <f t="shared" ref="J25" si="27">IF(I25="","",1440-I25)</f>
+        <v>840</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
@@ -2902,11 +2929,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="26">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="28">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="27">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="29">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -2924,11 +2951,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -2946,11 +2973,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -2968,11 +2995,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -2990,11 +3017,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3012,11 +3039,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3034,11 +3061,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3056,11 +3083,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3078,11 +3105,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3100,11 +3127,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3122,11 +3149,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3144,11 +3171,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3166,11 +3193,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3188,11 +3215,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3210,11 +3237,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3232,11 +3259,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3254,11 +3281,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3276,11 +3303,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3298,11 +3325,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3320,11 +3347,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3342,11 +3369,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3364,11 +3391,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3386,11 +3413,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3408,11 +3435,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3430,11 +3457,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3452,11 +3479,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3474,11 +3501,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3496,11 +3523,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3518,11 +3545,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3540,11 +3567,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3562,11 +3589,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3584,11 +3611,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3606,11 +3633,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3628,11 +3655,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3650,11 +3677,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3672,11 +3699,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3694,11 +3721,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3716,11 +3743,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3738,11 +3765,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3760,11 +3787,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3782,11 +3809,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3804,11 +3831,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3826,11 +3853,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3848,11 +3875,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3870,11 +3897,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3892,11 +3919,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3914,11 +3941,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -3936,11 +3963,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -3958,11 +3985,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -3980,11 +4007,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4002,11 +4029,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4024,11 +4051,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4046,11 +4073,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4068,11 +4095,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4090,11 +4117,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4112,11 +4139,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4134,11 +4161,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4156,11 +4183,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4178,11 +4205,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4200,11 +4227,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4222,11 +4249,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4244,11 +4271,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4266,11 +4293,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4288,11 +4315,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4310,11 +4337,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="28">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="30">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="29">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="31">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4332,11 +4359,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4354,11 +4381,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4376,11 +4403,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4398,11 +4425,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4420,11 +4447,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4442,11 +4469,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4464,11 +4491,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4486,11 +4513,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4508,11 +4535,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4530,11 +4557,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4552,11 +4579,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4574,11 +4601,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4596,11 +4623,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4618,11 +4645,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4640,11 +4667,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4662,11 +4689,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4684,11 +4711,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4706,11 +4733,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4728,11 +4755,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4750,11 +4777,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4772,11 +4799,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4794,11 +4821,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4816,11 +4843,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4838,11 +4865,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -4860,11 +4887,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -4882,11 +4909,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -4904,11 +4931,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -4926,11 +4953,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -4948,11 +4975,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -4970,11 +4997,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -4992,11 +5019,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5014,11 +5041,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5036,11 +5063,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5058,11 +5085,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5080,11 +5107,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5102,11 +5129,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5124,11 +5151,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5146,11 +5173,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5168,11 +5195,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5190,11 +5217,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5212,11 +5239,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5234,11 +5261,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5256,11 +5283,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5278,11 +5305,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5300,11 +5327,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5322,11 +5349,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5344,11 +5371,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5366,11 +5393,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5388,11 +5415,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5410,11 +5437,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5432,11 +5459,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5454,11 +5481,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5476,11 +5503,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5498,11 +5525,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5520,11 +5547,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5542,11 +5569,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5564,11 +5591,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5586,11 +5613,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5608,11 +5635,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5630,11 +5657,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5652,11 +5679,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5674,11 +5701,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5696,11 +5723,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5718,11 +5745,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="30">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="32">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="31">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="33">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5740,11 +5767,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5762,11 +5789,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5784,11 +5811,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5806,11 +5833,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5828,11 +5855,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -5850,11 +5877,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -5872,11 +5899,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -5894,11 +5921,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -5916,11 +5943,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -5938,11 +5965,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -5960,11 +5987,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -5982,11 +6009,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6004,11 +6031,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6026,11 +6053,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6048,11 +6075,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6070,11 +6097,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6092,11 +6119,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6114,11 +6141,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6136,11 +6163,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6158,11 +6185,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6180,11 +6207,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6202,11 +6229,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6224,11 +6251,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6246,11 +6273,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6268,11 +6295,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6290,11 +6317,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6312,11 +6339,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6334,11 +6361,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6356,11 +6383,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6378,11 +6405,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6400,11 +6427,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6422,11 +6449,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6444,11 +6471,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6466,11 +6493,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6488,11 +6515,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6510,11 +6537,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6532,11 +6559,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6554,11 +6581,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6576,11 +6603,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6598,11 +6625,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6620,11 +6647,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6642,11 +6669,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6664,11 +6691,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6686,11 +6713,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6708,11 +6735,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6730,11 +6757,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6752,11 +6779,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6774,11 +6801,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6796,11 +6823,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6818,11 +6845,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6840,11 +6867,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -6862,11 +6889,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -6884,11 +6911,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -6906,11 +6933,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -6928,11 +6955,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -6950,11 +6977,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -6972,11 +6999,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -6994,11 +7021,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7016,11 +7043,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7038,11 +7065,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7060,11 +7087,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7082,11 +7109,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7104,11 +7131,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7126,11 +7153,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="32">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="34">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="33">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="35">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7148,11 +7175,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7170,11 +7197,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7192,11 +7219,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7214,11 +7241,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7236,11 +7263,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7258,11 +7285,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7280,11 +7307,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7302,11 +7329,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7324,11 +7351,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7346,11 +7373,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7368,11 +7395,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7390,11 +7417,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7412,11 +7439,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7434,11 +7461,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7456,11 +7483,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7478,11 +7505,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7500,11 +7527,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7522,11 +7549,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7544,11 +7571,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7566,11 +7593,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7588,11 +7615,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7610,11 +7637,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7632,11 +7659,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7654,11 +7681,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7676,11 +7703,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7698,11 +7725,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7720,11 +7747,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7742,11 +7769,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7764,11 +7791,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7786,11 +7813,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7808,11 +7835,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7830,11 +7857,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -7852,11 +7879,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -7874,11 +7901,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -7896,11 +7923,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -7918,11 +7945,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -7940,11 +7967,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -7962,11 +7989,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -7984,11 +8011,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8006,11 +8033,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8028,11 +8055,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8050,11 +8077,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8072,11 +8099,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8094,11 +8121,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8116,11 +8143,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8138,11 +8165,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8160,11 +8187,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8182,11 +8209,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8204,11 +8231,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8226,11 +8253,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8248,11 +8275,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8270,11 +8297,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8292,11 +8319,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8314,11 +8341,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8336,11 +8363,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8358,11 +8385,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8380,11 +8407,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8402,11 +8429,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8424,11 +8451,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8446,11 +8473,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8468,11 +8495,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8490,11 +8517,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8512,11 +8539,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8534,11 +8561,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="34">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="36">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="35">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="37">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8556,11 +8583,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8578,11 +8605,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8600,11 +8627,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8622,11 +8649,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8644,11 +8671,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8666,11 +8693,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8688,11 +8715,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8710,11 +8737,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8732,11 +8759,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8754,11 +8781,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8776,11 +8803,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8798,11 +8825,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8820,11 +8847,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8842,11 +8869,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -8864,11 +8891,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -8886,11 +8913,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -8908,11 +8935,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -8930,11 +8957,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -8952,11 +8979,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -8974,11 +9001,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -8996,11 +9023,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9018,11 +9045,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9040,11 +9067,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9062,11 +9089,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9084,11 +9111,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9106,11 +9133,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9128,11 +9155,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9150,11 +9177,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9172,11 +9199,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9194,11 +9221,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9216,11 +9243,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9238,11 +9265,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9260,11 +9287,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9282,11 +9309,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9304,11 +9331,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9326,11 +9353,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9348,11 +9375,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9370,11 +9397,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9392,11 +9419,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9414,11 +9441,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9436,11 +9463,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9458,11 +9485,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9480,11 +9507,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9502,11 +9529,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9524,11 +9551,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9546,11 +9573,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9568,11 +9595,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9590,11 +9617,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9612,11 +9639,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9634,11 +9661,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9656,11 +9683,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9678,11 +9705,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9700,11 +9727,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9722,11 +9749,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9744,11 +9771,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9766,11 +9793,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9788,11 +9815,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9810,11 +9837,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -9832,11 +9859,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -9854,11 +9881,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -9876,11 +9903,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -9898,11 +9925,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -9920,11 +9947,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -9942,11 +9969,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="36">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="38">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="37">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="39">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -9964,11 +9991,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -9986,11 +10013,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10008,11 +10035,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10030,11 +10057,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10052,11 +10079,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10074,11 +10101,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10096,11 +10123,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10118,11 +10145,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10140,11 +10167,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10162,11 +10189,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10184,11 +10211,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE798647-8EB0-4BD8-90EE-C53601B2EF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2312730F-2B9C-4934-9FE9-57BD37EEEE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Today, I worked on CA Practice and College Subjects.</t>
+  </si>
+  <si>
+    <t>Today, I worked on SQL and College Subjects.</t>
   </si>
 </sst>
 </file>
@@ -1951,27 +1954,51 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="12"/>
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B26" s="14">
+        <v>450</v>
+      </c>
+      <c r="C26" s="14">
+        <v>20</v>
+      </c>
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>120</v>
+      </c>
+      <c r="F26" s="14">
+        <v>350</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
+        <f t="shared" ref="I26" si="28">IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
+        <v>1120</v>
+      </c>
+      <c r="J26" s="15">
+        <f t="shared" ref="J26" si="29">IF(I26="","",1440-I26)</f>
+        <v>320</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
@@ -2929,11 +2956,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="28">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="30">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="29">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="31">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -2951,11 +2978,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -2973,11 +3000,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -2995,11 +3022,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3017,11 +3044,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3039,11 +3066,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3061,11 +3088,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3083,11 +3110,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3105,11 +3132,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3127,11 +3154,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3149,11 +3176,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3171,11 +3198,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3193,11 +3220,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3215,11 +3242,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3237,11 +3264,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3259,11 +3286,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3281,11 +3308,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3303,11 +3330,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3325,11 +3352,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3347,11 +3374,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3369,11 +3396,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3391,11 +3418,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3413,11 +3440,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3435,11 +3462,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3457,11 +3484,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3479,11 +3506,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3501,11 +3528,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3523,11 +3550,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3545,11 +3572,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3567,11 +3594,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3589,11 +3616,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3611,11 +3638,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3633,11 +3660,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3655,11 +3682,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3677,11 +3704,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3699,11 +3726,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3721,11 +3748,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3743,11 +3770,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3765,11 +3792,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3787,11 +3814,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3809,11 +3836,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3831,11 +3858,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3853,11 +3880,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3875,11 +3902,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3897,11 +3924,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3919,11 +3946,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3941,11 +3968,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -3963,11 +3990,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -3985,11 +4012,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4007,11 +4034,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4029,11 +4056,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4051,11 +4078,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4073,11 +4100,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4095,11 +4122,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4117,11 +4144,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4139,11 +4166,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4161,11 +4188,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4183,11 +4210,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4205,11 +4232,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4227,11 +4254,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4249,11 +4276,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4271,11 +4298,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4293,11 +4320,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4315,11 +4342,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4337,11 +4364,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="30">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="32">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="31">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="33">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4359,11 +4386,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4381,11 +4408,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4403,11 +4430,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4425,11 +4452,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4447,11 +4474,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4469,11 +4496,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4491,11 +4518,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4513,11 +4540,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4535,11 +4562,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4557,11 +4584,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4579,11 +4606,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4601,11 +4628,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4623,11 +4650,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4645,11 +4672,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4667,11 +4694,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4689,11 +4716,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4711,11 +4738,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4733,11 +4760,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4755,11 +4782,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4777,11 +4804,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4799,11 +4826,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4821,11 +4848,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4843,11 +4870,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4865,11 +4892,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -4887,11 +4914,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -4909,11 +4936,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -4931,11 +4958,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -4953,11 +4980,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -4975,11 +5002,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -4997,11 +5024,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5019,11 +5046,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5041,11 +5068,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5063,11 +5090,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5085,11 +5112,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5107,11 +5134,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5129,11 +5156,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5151,11 +5178,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5173,11 +5200,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5195,11 +5222,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5217,11 +5244,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5239,11 +5266,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5261,11 +5288,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5283,11 +5310,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5305,11 +5332,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5327,11 +5354,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5349,11 +5376,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5371,11 +5398,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5393,11 +5420,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5415,11 +5442,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5437,11 +5464,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5459,11 +5486,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5481,11 +5508,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5503,11 +5530,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5525,11 +5552,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5547,11 +5574,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5569,11 +5596,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5591,11 +5618,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5613,11 +5640,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5635,11 +5662,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5657,11 +5684,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5679,11 +5706,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5701,11 +5728,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5723,11 +5750,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5745,11 +5772,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="32">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="34">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="33">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="35">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5767,11 +5794,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5789,11 +5816,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5811,11 +5838,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5833,11 +5860,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5855,11 +5882,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -5877,11 +5904,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -5899,11 +5926,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -5921,11 +5948,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -5943,11 +5970,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -5965,11 +5992,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -5987,11 +6014,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6009,11 +6036,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6031,11 +6058,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6053,11 +6080,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6075,11 +6102,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6097,11 +6124,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6119,11 +6146,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6141,11 +6168,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6163,11 +6190,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6185,11 +6212,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6207,11 +6234,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6229,11 +6256,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6251,11 +6278,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6273,11 +6300,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6295,11 +6322,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6317,11 +6344,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6339,11 +6366,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6361,11 +6388,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6383,11 +6410,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6405,11 +6432,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6427,11 +6454,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6449,11 +6476,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6471,11 +6498,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6493,11 +6520,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6515,11 +6542,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6537,11 +6564,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6559,11 +6586,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6581,11 +6608,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6603,11 +6630,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6625,11 +6652,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6647,11 +6674,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6669,11 +6696,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6691,11 +6718,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6713,11 +6740,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6735,11 +6762,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6757,11 +6784,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6779,11 +6806,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6801,11 +6828,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6823,11 +6850,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6845,11 +6872,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6867,11 +6894,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -6889,11 +6916,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -6911,11 +6938,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -6933,11 +6960,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -6955,11 +6982,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -6977,11 +7004,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -6999,11 +7026,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7021,11 +7048,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7043,11 +7070,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7065,11 +7092,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7087,11 +7114,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7109,11 +7136,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7131,11 +7158,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7153,11 +7180,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="34">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="36">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="35">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="37">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7175,11 +7202,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7197,11 +7224,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7219,11 +7246,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7241,11 +7268,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7263,11 +7290,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7285,11 +7312,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7307,11 +7334,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7329,11 +7356,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7351,11 +7378,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7373,11 +7400,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7395,11 +7422,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7417,11 +7444,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7439,11 +7466,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7461,11 +7488,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7483,11 +7510,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7505,11 +7532,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7527,11 +7554,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7549,11 +7576,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7571,11 +7598,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7593,11 +7620,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7615,11 +7642,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7637,11 +7664,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7659,11 +7686,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7681,11 +7708,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7703,11 +7730,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7725,11 +7752,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7747,11 +7774,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7769,11 +7796,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7791,11 +7818,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7813,11 +7840,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7835,11 +7862,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7857,11 +7884,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -7879,11 +7906,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -7901,11 +7928,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -7923,11 +7950,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -7945,11 +7972,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -7967,11 +7994,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -7989,11 +8016,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8011,11 +8038,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8033,11 +8060,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8055,11 +8082,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8077,11 +8104,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8099,11 +8126,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8121,11 +8148,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8143,11 +8170,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8165,11 +8192,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8187,11 +8214,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8209,11 +8236,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8231,11 +8258,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8253,11 +8280,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8275,11 +8302,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8297,11 +8324,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8319,11 +8346,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8341,11 +8368,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8363,11 +8390,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8385,11 +8412,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8407,11 +8434,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8429,11 +8456,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8451,11 +8478,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8473,11 +8500,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8495,11 +8522,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8517,11 +8544,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8539,11 +8566,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8561,11 +8588,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="36">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="38">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="37">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="39">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8583,11 +8610,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8605,11 +8632,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8627,11 +8654,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8649,11 +8676,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8671,11 +8698,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8693,11 +8720,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8715,11 +8742,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8737,11 +8764,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8759,11 +8786,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8781,11 +8808,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8803,11 +8830,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8825,11 +8852,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8847,11 +8874,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8869,11 +8896,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -8891,11 +8918,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -8913,11 +8940,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -8935,11 +8962,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -8957,11 +8984,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -8979,11 +9006,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9001,11 +9028,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9023,11 +9050,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9045,11 +9072,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9067,11 +9094,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9089,11 +9116,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9111,11 +9138,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9133,11 +9160,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9155,11 +9182,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9177,11 +9204,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9199,11 +9226,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9221,11 +9248,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9243,11 +9270,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9265,11 +9292,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9287,11 +9314,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9309,11 +9336,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9331,11 +9358,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9353,11 +9380,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9375,11 +9402,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9397,11 +9424,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9419,11 +9446,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9441,11 +9468,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9463,11 +9490,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9485,11 +9512,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9507,11 +9534,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9529,11 +9556,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9551,11 +9578,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9573,11 +9600,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9595,11 +9622,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9617,11 +9644,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9639,11 +9666,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9661,11 +9688,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9683,11 +9710,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9705,11 +9732,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9727,11 +9754,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9749,11 +9776,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9771,11 +9798,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9793,11 +9820,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9815,11 +9842,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9837,11 +9864,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -9859,11 +9886,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -9881,11 +9908,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -9903,11 +9930,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -9925,11 +9952,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -9947,11 +9974,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -9969,11 +9996,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="38">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="40">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="39">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="41">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -9991,11 +10018,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10013,11 +10040,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10035,11 +10062,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10057,11 +10084,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10079,11 +10106,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10101,11 +10128,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10123,11 +10150,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10145,11 +10172,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10167,11 +10194,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10189,11 +10216,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10211,11 +10238,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2312730F-2B9C-4934-9FE9-57BD37EEEE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B1FD27-E537-4069-9500-BFB9B9200E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>Today, I worked on SQL and College Subjects.</t>
+  </si>
+  <si>
+    <t>Today, I worked on College Subjects.</t>
   </si>
 </sst>
 </file>
@@ -2000,27 +2003,51 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="12"/>
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B27" s="14">
+        <v>450</v>
+      </c>
+      <c r="C27" s="14">
+        <v>30</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>30</v>
+      </c>
+      <c r="F27" s="14">
+        <v>300</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="14">
+        <v>60</v>
+      </c>
+      <c r="I27" s="15">
+        <f t="shared" ref="I27" si="30">IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
+        <v>990</v>
+      </c>
+      <c r="J27" s="15">
+        <f t="shared" ref="J27" si="31">IF(I27="","",1440-I27)</f>
+        <v>450</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
@@ -2956,11 +2983,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="30">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="32">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="31">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="33">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -2978,11 +3005,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3000,11 +3027,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3022,11 +3049,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3044,11 +3071,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3066,11 +3093,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3088,11 +3115,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3110,11 +3137,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3132,11 +3159,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3154,11 +3181,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3176,11 +3203,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3198,11 +3225,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3220,11 +3247,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3242,11 +3269,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3264,11 +3291,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3286,11 +3313,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3308,11 +3335,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3330,11 +3357,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3352,11 +3379,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3374,11 +3401,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3396,11 +3423,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3418,11 +3445,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3440,11 +3467,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3462,11 +3489,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3484,11 +3511,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3506,11 +3533,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3528,11 +3555,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3550,11 +3577,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3572,11 +3599,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3594,11 +3621,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3616,11 +3643,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3638,11 +3665,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3660,11 +3687,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3682,11 +3709,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3704,11 +3731,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3726,11 +3753,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3748,11 +3775,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3770,11 +3797,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3792,11 +3819,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3814,11 +3841,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3836,11 +3863,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3858,11 +3885,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3880,11 +3907,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3902,11 +3929,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3924,11 +3951,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3946,11 +3973,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3968,11 +3995,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -3990,11 +4017,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4012,11 +4039,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4034,11 +4061,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4056,11 +4083,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4078,11 +4105,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4100,11 +4127,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4122,11 +4149,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4144,11 +4171,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4166,11 +4193,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4188,11 +4215,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4210,11 +4237,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4232,11 +4259,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4254,11 +4281,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4276,11 +4303,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4298,11 +4325,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4320,11 +4347,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4342,11 +4369,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4364,11 +4391,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="32">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="34">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="33">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="35">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4386,11 +4413,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4408,11 +4435,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4430,11 +4457,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4452,11 +4479,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4474,11 +4501,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4496,11 +4523,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4518,11 +4545,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4540,11 +4567,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4562,11 +4589,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4584,11 +4611,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4606,11 +4633,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4628,11 +4655,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4650,11 +4677,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4672,11 +4699,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4694,11 +4721,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4716,11 +4743,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4738,11 +4765,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4760,11 +4787,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4782,11 +4809,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4804,11 +4831,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4826,11 +4853,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4848,11 +4875,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4870,11 +4897,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4892,11 +4919,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -4914,11 +4941,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -4936,11 +4963,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -4958,11 +4985,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -4980,11 +5007,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5002,11 +5029,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5024,11 +5051,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5046,11 +5073,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5068,11 +5095,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5090,11 +5117,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5112,11 +5139,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5134,11 +5161,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5156,11 +5183,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5178,11 +5205,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5200,11 +5227,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5222,11 +5249,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5244,11 +5271,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5266,11 +5293,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5288,11 +5315,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5310,11 +5337,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5332,11 +5359,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5354,11 +5381,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5376,11 +5403,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5398,11 +5425,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5420,11 +5447,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5442,11 +5469,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5464,11 +5491,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5486,11 +5513,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5508,11 +5535,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5530,11 +5557,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5552,11 +5579,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5574,11 +5601,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5596,11 +5623,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5618,11 +5645,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5640,11 +5667,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5662,11 +5689,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5684,11 +5711,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5706,11 +5733,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5728,11 +5755,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5750,11 +5777,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5772,11 +5799,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="34">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="36">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="35">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="37">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5794,11 +5821,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5816,11 +5843,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5838,11 +5865,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5860,11 +5887,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5882,11 +5909,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -5904,11 +5931,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -5926,11 +5953,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -5948,11 +5975,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -5970,11 +5997,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -5992,11 +6019,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6014,11 +6041,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6036,11 +6063,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6058,11 +6085,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6080,11 +6107,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6102,11 +6129,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6124,11 +6151,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6146,11 +6173,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6168,11 +6195,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6190,11 +6217,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6212,11 +6239,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6234,11 +6261,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6256,11 +6283,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6278,11 +6305,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6300,11 +6327,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6322,11 +6349,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6344,11 +6371,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6366,11 +6393,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6388,11 +6415,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6410,11 +6437,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6432,11 +6459,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6454,11 +6481,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6476,11 +6503,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6498,11 +6525,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6520,11 +6547,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6542,11 +6569,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6564,11 +6591,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6586,11 +6613,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6608,11 +6635,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6630,11 +6657,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6652,11 +6679,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6674,11 +6701,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6696,11 +6723,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6718,11 +6745,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6740,11 +6767,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6762,11 +6789,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6784,11 +6811,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6806,11 +6833,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6828,11 +6855,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6850,11 +6877,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6872,11 +6899,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6894,11 +6921,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -6916,11 +6943,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -6938,11 +6965,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -6960,11 +6987,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -6982,11 +7009,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7004,11 +7031,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7026,11 +7053,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7048,11 +7075,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7070,11 +7097,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7092,11 +7119,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7114,11 +7141,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7136,11 +7163,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7158,11 +7185,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7180,11 +7207,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="36">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="38">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="37">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="39">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7202,11 +7229,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7224,11 +7251,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7246,11 +7273,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7268,11 +7295,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7290,11 +7317,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7312,11 +7339,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7334,11 +7361,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7356,11 +7383,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7378,11 +7405,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7400,11 +7427,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7422,11 +7449,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7444,11 +7471,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7466,11 +7493,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7488,11 +7515,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7510,11 +7537,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7532,11 +7559,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7554,11 +7581,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7576,11 +7603,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7598,11 +7625,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7620,11 +7647,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7642,11 +7669,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7664,11 +7691,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7686,11 +7713,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7708,11 +7735,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7730,11 +7757,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7752,11 +7779,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7774,11 +7801,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7796,11 +7823,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7818,11 +7845,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7840,11 +7867,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7862,11 +7889,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7884,11 +7911,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -7906,11 +7933,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -7928,11 +7955,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -7950,11 +7977,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -7972,11 +7999,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -7994,11 +8021,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8016,11 +8043,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8038,11 +8065,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8060,11 +8087,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8082,11 +8109,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8104,11 +8131,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8126,11 +8153,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8148,11 +8175,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8170,11 +8197,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8192,11 +8219,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8214,11 +8241,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8236,11 +8263,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8258,11 +8285,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8280,11 +8307,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8302,11 +8329,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8324,11 +8351,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8346,11 +8373,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8368,11 +8395,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8390,11 +8417,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8412,11 +8439,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8434,11 +8461,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8456,11 +8483,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8478,11 +8505,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8500,11 +8527,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8522,11 +8549,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8544,11 +8571,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8566,11 +8593,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8588,11 +8615,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="38">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="40">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="39">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="41">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8610,11 +8637,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8632,11 +8659,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8654,11 +8681,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8676,11 +8703,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8698,11 +8725,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8720,11 +8747,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8742,11 +8769,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8764,11 +8791,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8786,11 +8813,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8808,11 +8835,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8830,11 +8857,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8852,11 +8879,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8874,11 +8901,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8896,11 +8923,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -8918,11 +8945,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -8940,11 +8967,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -8962,11 +8989,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -8984,11 +9011,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9006,11 +9033,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9028,11 +9055,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9050,11 +9077,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9072,11 +9099,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9094,11 +9121,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9116,11 +9143,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9138,11 +9165,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9160,11 +9187,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9182,11 +9209,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9204,11 +9231,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9226,11 +9253,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9248,11 +9275,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9270,11 +9297,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9292,11 +9319,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9314,11 +9341,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9336,11 +9363,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9358,11 +9385,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9380,11 +9407,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9402,11 +9429,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9424,11 +9451,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9446,11 +9473,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9468,11 +9495,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9490,11 +9517,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9512,11 +9539,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9534,11 +9561,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9556,11 +9583,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9578,11 +9605,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9600,11 +9627,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9622,11 +9649,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9644,11 +9671,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9666,11 +9693,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9688,11 +9715,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9710,11 +9737,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9732,11 +9759,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9754,11 +9781,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9776,11 +9803,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9798,11 +9825,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9820,11 +9847,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9842,11 +9869,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9864,11 +9891,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -9886,11 +9913,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -9908,11 +9935,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -9930,11 +9957,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -9952,11 +9979,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -9974,11 +10001,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -9996,11 +10023,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="40">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="42">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="41">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="43">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10018,11 +10045,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10040,11 +10067,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10062,11 +10089,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10084,11 +10111,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10106,11 +10133,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10128,11 +10155,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10150,11 +10177,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10172,11 +10199,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10194,11 +10221,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10216,11 +10243,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10238,11 +10265,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B1FD27-E537-4069-9500-BFB9B9200E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2B246D-CA72-4531-A716-8DF7BB4E6F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2049,27 +2049,51 @@
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="12"/>
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B28" s="14">
+        <v>450</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>120</v>
+      </c>
+      <c r="E28" s="14">
+        <v>40</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>60</v>
+      </c>
+      <c r="I28" s="15">
+        <f t="shared" ref="I28" si="32">IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
+        <v>1050</v>
+      </c>
+      <c r="J28" s="15">
+        <f t="shared" ref="J28" si="33">IF(I28="","",1440-I28)</f>
+        <v>390</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
@@ -2983,11 +3007,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="32">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="34">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="33">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="35">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3005,11 +3029,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3027,11 +3051,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3049,11 +3073,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3071,11 +3095,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3093,11 +3117,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3115,11 +3139,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3137,11 +3161,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3159,11 +3183,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3181,11 +3205,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3203,11 +3227,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3225,11 +3249,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3247,11 +3271,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3269,11 +3293,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3291,11 +3315,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3313,11 +3337,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3335,11 +3359,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3357,11 +3381,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3379,11 +3403,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3401,11 +3425,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3423,11 +3447,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3445,11 +3469,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3467,11 +3491,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3489,11 +3513,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3511,11 +3535,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3533,11 +3557,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3555,11 +3579,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3577,11 +3601,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3599,11 +3623,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3621,11 +3645,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3643,11 +3667,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3665,11 +3689,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3687,11 +3711,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3709,11 +3733,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3731,11 +3755,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3753,11 +3777,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3775,11 +3799,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3797,11 +3821,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3819,11 +3843,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3841,11 +3865,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3863,11 +3887,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3885,11 +3909,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3907,11 +3931,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3929,11 +3953,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3951,11 +3975,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3973,11 +3997,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3995,11 +4019,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4017,11 +4041,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4039,11 +4063,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4061,11 +4085,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4083,11 +4107,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4105,11 +4129,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4127,11 +4151,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4149,11 +4173,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4171,11 +4195,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4193,11 +4217,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4215,11 +4239,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4237,11 +4261,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4259,11 +4283,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4281,11 +4305,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4303,11 +4327,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4325,11 +4349,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4347,11 +4371,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4369,11 +4393,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4391,11 +4415,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="34">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="36">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="35">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="37">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4413,11 +4437,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4435,11 +4459,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4457,11 +4481,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4479,11 +4503,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4501,11 +4525,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4523,11 +4547,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4545,11 +4569,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4567,11 +4591,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4589,11 +4613,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4611,11 +4635,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4633,11 +4657,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4655,11 +4679,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4677,11 +4701,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4699,11 +4723,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4721,11 +4745,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4743,11 +4767,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4765,11 +4789,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4787,11 +4811,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4809,11 +4833,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4831,11 +4855,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4853,11 +4877,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4875,11 +4899,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4897,11 +4921,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4919,11 +4943,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -4941,11 +4965,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -4963,11 +4987,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -4985,11 +5009,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5007,11 +5031,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5029,11 +5053,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5051,11 +5075,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5073,11 +5097,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5095,11 +5119,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5117,11 +5141,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5139,11 +5163,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5161,11 +5185,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5183,11 +5207,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5205,11 +5229,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5227,11 +5251,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5249,11 +5273,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5271,11 +5295,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5293,11 +5317,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5315,11 +5339,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5337,11 +5361,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5359,11 +5383,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5381,11 +5405,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5403,11 +5427,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5425,11 +5449,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5447,11 +5471,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5469,11 +5493,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5491,11 +5515,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5513,11 +5537,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5535,11 +5559,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5557,11 +5581,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5579,11 +5603,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5601,11 +5625,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5623,11 +5647,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5645,11 +5669,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5667,11 +5691,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5689,11 +5713,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5711,11 +5735,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5733,11 +5757,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5755,11 +5779,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5777,11 +5801,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5799,11 +5823,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="36">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="38">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="37">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="39">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5821,11 +5845,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5843,11 +5867,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5865,11 +5889,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5887,11 +5911,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5909,11 +5933,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -5931,11 +5955,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -5953,11 +5977,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -5975,11 +5999,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -5997,11 +6021,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6019,11 +6043,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6041,11 +6065,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6063,11 +6087,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6085,11 +6109,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6107,11 +6131,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6129,11 +6153,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6151,11 +6175,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6173,11 +6197,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6195,11 +6219,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6217,11 +6241,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6239,11 +6263,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6261,11 +6285,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6283,11 +6307,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6305,11 +6329,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6327,11 +6351,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6349,11 +6373,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6371,11 +6395,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6393,11 +6417,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6415,11 +6439,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6437,11 +6461,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6459,11 +6483,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6481,11 +6505,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6503,11 +6527,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6525,11 +6549,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6547,11 +6571,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6569,11 +6593,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6591,11 +6615,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6613,11 +6637,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6635,11 +6659,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6657,11 +6681,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6679,11 +6703,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6701,11 +6725,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6723,11 +6747,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6745,11 +6769,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6767,11 +6791,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6789,11 +6813,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6811,11 +6835,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6833,11 +6857,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6855,11 +6879,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6877,11 +6901,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6899,11 +6923,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6921,11 +6945,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -6943,11 +6967,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -6965,11 +6989,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -6987,11 +7011,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7009,11 +7033,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7031,11 +7055,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7053,11 +7077,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7075,11 +7099,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7097,11 +7121,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7119,11 +7143,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7141,11 +7165,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7163,11 +7187,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7185,11 +7209,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7207,11 +7231,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="38">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="40">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="39">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="41">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7229,11 +7253,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7251,11 +7275,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7273,11 +7297,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7295,11 +7319,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7317,11 +7341,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7339,11 +7363,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7361,11 +7385,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7383,11 +7407,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7405,11 +7429,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7427,11 +7451,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7449,11 +7473,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7471,11 +7495,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7493,11 +7517,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7515,11 +7539,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7537,11 +7561,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7559,11 +7583,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7581,11 +7605,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7603,11 +7627,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7625,11 +7649,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7647,11 +7671,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7669,11 +7693,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7691,11 +7715,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7713,11 +7737,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7735,11 +7759,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7757,11 +7781,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7779,11 +7803,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7801,11 +7825,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7823,11 +7847,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7845,11 +7869,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7867,11 +7891,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7889,11 +7913,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7911,11 +7935,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -7933,11 +7957,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -7955,11 +7979,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -7977,11 +8001,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -7999,11 +8023,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8021,11 +8045,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8043,11 +8067,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8065,11 +8089,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8087,11 +8111,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8109,11 +8133,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8131,11 +8155,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8153,11 +8177,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8175,11 +8199,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8197,11 +8221,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8219,11 +8243,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8241,11 +8265,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8263,11 +8287,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8285,11 +8309,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8307,11 +8331,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8329,11 +8353,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8351,11 +8375,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8373,11 +8397,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8395,11 +8419,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8417,11 +8441,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8439,11 +8463,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8461,11 +8485,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8483,11 +8507,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8505,11 +8529,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8527,11 +8551,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8549,11 +8573,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8571,11 +8595,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8593,11 +8617,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8615,11 +8639,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="40">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="42">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="41">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="43">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8637,11 +8661,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8659,11 +8683,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8681,11 +8705,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8703,11 +8727,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8725,11 +8749,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8747,11 +8771,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8769,11 +8793,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8791,11 +8815,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8813,11 +8837,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8835,11 +8859,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8857,11 +8881,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8879,11 +8903,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8901,11 +8925,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8923,11 +8947,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -8945,11 +8969,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -8967,11 +8991,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -8989,11 +9013,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9011,11 +9035,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9033,11 +9057,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9055,11 +9079,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9077,11 +9101,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9099,11 +9123,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9121,11 +9145,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9143,11 +9167,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9165,11 +9189,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9187,11 +9211,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9209,11 +9233,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9231,11 +9255,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9253,11 +9277,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9275,11 +9299,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9297,11 +9321,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9319,11 +9343,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9341,11 +9365,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9363,11 +9387,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9385,11 +9409,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9407,11 +9431,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9429,11 +9453,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9451,11 +9475,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9473,11 +9497,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9495,11 +9519,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9517,11 +9541,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9539,11 +9563,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9561,11 +9585,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9583,11 +9607,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9605,11 +9629,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9627,11 +9651,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9649,11 +9673,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9671,11 +9695,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9693,11 +9717,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9715,11 +9739,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9737,11 +9761,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9759,11 +9783,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9781,11 +9805,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9803,11 +9827,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9825,11 +9849,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9847,11 +9871,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9869,11 +9893,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9891,11 +9915,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -9913,11 +9937,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -9935,11 +9959,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -9957,11 +9981,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -9979,11 +10003,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10001,11 +10025,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10023,11 +10047,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="42">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="44">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="43">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="45">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10045,11 +10069,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10067,11 +10091,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10089,11 +10113,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10111,11 +10135,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10133,11 +10157,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10155,11 +10179,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10177,11 +10201,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10199,11 +10223,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10221,11 +10245,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10243,11 +10267,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10265,11 +10289,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12625731.xlsx
+++ b/12625731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2B246D-CA72-4531-A716-8DF7BB4E6F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C14852-B409-4E5B-AAD8-60493D12287D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2095,27 +2095,51 @@
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="12"/>
+    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B29" s="14">
+        <v>450</v>
+      </c>
+      <c r="C29" s="14">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
+        <v>130</v>
+      </c>
+      <c r="E29" s="14">
+        <v>20</v>
+      </c>
+      <c r="F29" s="14">
+        <v>350</v>
+      </c>
+      <c r="G29" s="14">
+        <v>7</v>
+      </c>
+      <c r="H29" s="14">
+        <v>60</v>
+      </c>
+      <c r="I29" s="15">
+        <f t="shared" ref="I29" si="34">IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
+        <v>1030</v>
+      </c>
+      <c r="J29" s="15">
+        <f t="shared" ref="J29" si="35">IF(I29="","",1440-I29)</f>
+        <v>410</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
@@ -3007,11 +3031,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="34">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="36">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="35">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="37">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3029,11 +3053,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3051,11 +3075,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3073,11 +3097,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3095,11 +3119,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3117,11 +3141,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3139,11 +3163,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3161,11 +3185,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3183,11 +3207,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3205,11 +3229,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3227,11 +3251,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3249,11 +3273,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3271,11 +3295,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3293,11 +3317,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3315,11 +3339,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3337,11 +3361,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3359,11 +3383,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3381,11 +3405,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3403,11 +3427,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3425,11 +3449,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3447,11 +3471,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3469,11 +3493,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3491,11 +3515,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3513,11 +3537,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3535,11 +3559,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3557,11 +3581,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3579,11 +3603,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3601,11 +3625,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3623,11 +3647,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3645,11 +3669,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3667,11 +3691,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3689,11 +3713,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3711,11 +3735,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3733,11 +3757,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3755,11 +3779,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3777,11 +3801,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3799,11 +3823,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3821,11 +3845,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3843,11 +3867,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3865,11 +3889,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3887,11 +3911,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3909,11 +3933,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3931,11 +3955,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3953,11 +3977,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3975,11 +3999,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3997,11 +4021,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4019,11 +4043,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4041,11 +4065,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4063,11 +4087,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4085,11 +4109,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4107,11 +4131,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4129,11 +4153,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4151,11 +4175,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4173,11 +4197,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4195,11 +4219,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4217,11 +4241,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4239,11 +4263,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4261,11 +4285,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4283,11 +4307,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4305,11 +4329,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4327,11 +4351,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4349,11 +4373,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4371,11 +4395,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4393,11 +4417,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4415,11 +4439,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="36">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="38">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="37">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="39">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4437,11 +4461,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4459,11 +4483,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4481,11 +4505,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4503,11 +4527,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4525,11 +4549,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4547,11 +4571,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4569,11 +4593,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4591,11 +4615,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4613,11 +4637,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4635,11 +4659,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4657,11 +4681,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4679,11 +4703,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4701,11 +4725,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4723,11 +4747,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4745,11 +4769,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4767,11 +4791,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4789,11 +4813,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4811,11 +4835,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4833,11 +4857,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4855,11 +4879,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4877,11 +4901,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4899,11 +4923,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4921,11 +4945,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4943,11 +4967,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -4965,11 +4989,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -4987,11 +5011,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5009,11 +5033,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5031,11 +5055,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5053,11 +5077,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5075,11 +5099,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5097,11 +5121,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5119,11 +5143,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5141,11 +5165,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5163,11 +5187,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5185,11 +5209,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5207,11 +5231,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5229,11 +5253,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5251,11 +5275,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5273,11 +5297,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5295,11 +5319,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5317,11 +5341,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5339,11 +5363,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5361,11 +5385,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5383,11 +5407,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5405,11 +5429,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5427,11 +5451,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5449,11 +5473,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5471,11 +5495,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5493,11 +5517,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5515,11 +5539,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5537,11 +5561,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5559,11 +5583,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5581,11 +5605,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5603,11 +5627,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5625,11 +5649,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5647,11 +5671,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5669,11 +5693,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5691,11 +5715,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5713,11 +5737,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5735,11 +5759,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5757,11 +5781,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5779,11 +5803,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5801,11 +5825,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5823,11 +5847,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="38">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="40">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="39">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="41">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5845,11 +5869,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5867,11 +5891,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5889,11 +5913,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5911,11 +5935,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5933,11 +5957,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -5955,11 +5979,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -5977,11 +6001,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -5999,11 +6023,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6021,11 +6045,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6043,11 +6067,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6065,11 +6089,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6087,11 +6111,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6109,11 +6133,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6131,11 +6155,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6153,11 +6177,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6175,11 +6199,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6197,11 +6221,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6219,11 +6243,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6241,11 +6265,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6263,11 +6287,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6285,11 +6309,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6307,11 +6331,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6329,11 +6353,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6351,11 +6375,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6373,11 +6397,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6395,11 +6419,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6417,11 +6441,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6439,11 +6463,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6461,11 +6485,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6483,11 +6507,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6505,11 +6529,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6527,11 +6551,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6549,11 +6573,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6571,11 +6595,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6593,11 +6617,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6615,11 +6639,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6637,11 +6661,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6659,11 +6683,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6681,11 +6705,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6703,11 +6727,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6725,11 +6749,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6747,11 +6771,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6769,11 +6793,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6791,11 +6815,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6813,11 +6837,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6835,11 +6859,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6857,11 +6881,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6879,11 +6903,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6901,11 +6925,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6923,11 +6947,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6945,11 +6969,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -6967,11 +6991,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -6989,11 +7013,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7011,11 +7035,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7033,11 +7057,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7055,11 +7079,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7077,11 +7101,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7099,11 +7123,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7121,11 +7145,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7143,11 +7167,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7165,11 +7189,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7187,11 +7211,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7209,11 +7233,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7231,11 +7255,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="40">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="42">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="41">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="43">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7253,11 +7277,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7275,11 +7299,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7297,11 +7321,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7319,11 +7343,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7341,11 +7365,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7363,11 +7387,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7385,11 +7409,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7407,11 +7431,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7429,11 +7453,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7451,11 +7475,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7473,11 +7497,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7495,11 +7519,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7517,11 +7541,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7539,11 +7563,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7561,11 +7585,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7583,11 +7607,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7605,11 +7629,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7627,11 +7651,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7649,11 +7673,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7671,11 +7695,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7693,11 +7717,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7715,11 +7739,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7737,11 +7761,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7759,11 +7783,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7781,11 +7805,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7803,11 +7827,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7825,11 +7849,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7847,11 +7871,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7869,11 +7893,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7891,11 +7915,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7913,11 +7937,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7935,11 +7959,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -7957,11 +7981,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -7979,11 +8003,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8001,11 +8025,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8023,11 +8047,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8045,11 +8069,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8067,11 +8091,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8089,11 +8113,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8111,11 +8135,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8133,11 +8157,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8155,11 +8179,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8177,11 +8201,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8199,11 +8223,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8221,11 +8245,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8243,11 +8267,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8265,11 +8289,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8287,11 +8311,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8309,11 +8333,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8331,11 +8355,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8353,11 +8377,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8375,11 +8399,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8397,11 +8421,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8419,11 +8443,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8441,11 +8465,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8463,11 +8487,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8485,11 +8509,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8507,11 +8531,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8529,11 +8553,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8551,11 +8575,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8573,11 +8597,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8595,11 +8619,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8617,11 +8641,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8639,11 +8663,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="42">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="44">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="43">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="45">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8661,11 +8685,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8683,11 +8707,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8705,11 +8729,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8727,11 +8751,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8749,11 +8773,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8771,11 +8795,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8793,11 +8817,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8815,11 +8839,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8837,11 +8861,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8859,11 +8883,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8881,11 +8905,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8903,11 +8927,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8925,11 +8949,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8947,11 +8971,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -8969,11 +8993,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -8991,11 +9015,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9013,11 +9037,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9035,11 +9059,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9057,11 +9081,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9079,11 +9103,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9101,11 +9125,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9123,11 +9147,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9145,11 +9169,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9167,11 +9191,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9189,11 +9213,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9211,11 +9235,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9233,11 +9257,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9255,11 +9279,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9277,11 +9301,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9299,11 +9323,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9321,11 +9345,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9343,11 +9367,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9365,11 +9389,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9387,11 +9411,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9409,11 +9433,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9431,11 +9455,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9453,11 +9477,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9475,11 +9499,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9497,11 +9521,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9519,11 +9543,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9541,11 +9565,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9563,11 +9587,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9585,11 +9609,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9607,11 +9631,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9629,11 +9653,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9651,11 +9675,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9673,11 +9697,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9695,11 +9719,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9717,11 +9741,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9739,11 +9763,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9761,11 +9785,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9783,11 +9807,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9805,11 +9829,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9827,11 +9851,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9849,11 +987